--- a/table/gold_standard_30_march.xlsx
+++ b/table/gold_standard_30_march.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangmengyao/Desktop/Github/policyclaims/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveuclac-my.sharepoint.com/personal/rmjldba_ucl_ac_uk/Documents/ideas/policy/abstract_analysis/paper/anonymised_aje/additional validation checks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C9CB1C-5C68-9345-A056-110692EA1228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E7DF9C8-E1B4-44D2-8755-57D84CD56F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16080" yWindow="-22480" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7120" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -3976,7 +3976,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4294,29 +4294,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB652"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="34.33203125" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="34.28515625" customWidth="1"/>
     <col min="3" max="3" width="14" hidden="1" customWidth="1"/>
-    <col min="4" max="6" width="8.83203125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="96.5" customWidth="1"/>
-    <col min="8" max="8" width="25.33203125" hidden="1" customWidth="1"/>
+    <col min="4" max="6" width="8.85546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="96.42578125" customWidth="1"/>
+    <col min="8" max="8" width="25.28515625" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="13" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="21.6640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="21.7109375" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="28.83203125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="25.6640625" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="11.83203125" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="23.33203125" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="11.83203125" customWidth="1"/>
-    <col min="18" max="25" width="8.83203125" customWidth="1"/>
-    <col min="26" max="26" width="41.6640625" customWidth="1"/>
-    <col min="27" max="27" width="84.33203125" customWidth="1"/>
+    <col min="12" max="12" width="28.85546875" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="25.7109375" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="23.28515625" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="11.85546875" customWidth="1"/>
+    <col min="18" max="22" width="8.85546875" customWidth="1"/>
+    <col min="23" max="23" width="47.28515625" customWidth="1"/>
+    <col min="24" max="25" width="8.85546875" customWidth="1"/>
+    <col min="26" max="26" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="84.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" ht="15.95">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4387,7 +4389,7 @@
       <c r="X1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Z1" s="11" t="s">
+      <c r="Z1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="AA1" s="11" t="s">
@@ -4397,7 +4399,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="240" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" ht="240">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -4460,7 +4462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="176" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28" ht="176.1">
       <c r="A3" s="1" t="s">
         <v>32</v>
       </c>
@@ -4529,7 +4531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="240" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" ht="240">
       <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
@@ -4592,7 +4594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" ht="409.6">
       <c r="A5" s="1" t="s">
         <v>46</v>
       </c>
@@ -4661,7 +4663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="160" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" ht="159.94999999999999">
       <c r="A6" s="1" t="s">
         <v>54</v>
       </c>
@@ -4724,7 +4726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" ht="32.1">
       <c r="A7" s="1" t="s">
         <v>59</v>
       </c>
@@ -4795,7 +4797,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="272" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" ht="272.10000000000002">
       <c r="A8" s="1" t="s">
         <v>69</v>
       </c>
@@ -4858,7 +4860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="224" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" ht="224.1">
       <c r="A9" s="1" t="s">
         <v>74</v>
       </c>
@@ -4921,7 +4923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="224" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" ht="224.1">
       <c r="A10" s="1" t="s">
         <v>81</v>
       </c>
@@ -4990,7 +4992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="64" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" ht="63.95">
       <c r="A11" s="1" t="s">
         <v>90</v>
       </c>
@@ -5057,7 +5059,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="80" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28" ht="80.099999999999994">
       <c r="A12" s="1" t="s">
         <v>94</v>
       </c>
@@ -5120,7 +5122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="144" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" ht="144">
       <c r="A13" s="1" t="s">
         <v>99</v>
       </c>
@@ -5183,7 +5185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="256" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28" ht="255.95">
       <c r="A14" s="1" t="s">
         <v>103</v>
       </c>
@@ -5252,7 +5254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="304" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" ht="303.95">
       <c r="A15" s="1" t="s">
         <v>113</v>
       </c>
@@ -5315,7 +5317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:28" ht="395" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" ht="395.1">
       <c r="A16" s="1" t="s">
         <v>117</v>
       </c>
@@ -5378,7 +5380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="160" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="159.94999999999999">
       <c r="A17" s="1" t="s">
         <v>123</v>
       </c>
@@ -5441,7 +5443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="224" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="224.1">
       <c r="A18" s="1" t="s">
         <v>129</v>
       </c>
@@ -5504,7 +5506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="208" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="207.95">
       <c r="A19" s="1" t="s">
         <v>135</v>
       </c>
@@ -5573,7 +5575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="208" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="207.95">
       <c r="A20" s="1" t="s">
         <v>143</v>
       </c>
@@ -5638,7 +5640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>149</v>
       </c>
@@ -5701,7 +5703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>155</v>
       </c>
@@ -5764,7 +5766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>160</v>
       </c>
@@ -5831,7 +5833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>167</v>
       </c>
@@ -5896,7 +5898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>172</v>
       </c>
@@ -5961,7 +5963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>176</v>
       </c>
@@ -6030,7 +6032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>185</v>
       </c>
@@ -6093,7 +6095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>190</v>
       </c>
@@ -6156,7 +6158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>195</v>
       </c>
@@ -6219,7 +6221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>199</v>
       </c>
@@ -6286,7 +6288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>203</v>
       </c>
@@ -6353,7 +6355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>208</v>
       </c>
@@ -6416,7 +6418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>214</v>
       </c>
@@ -6479,7 +6481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>220</v>
       </c>
@@ -6542,7 +6544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" ht="15.75" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>224</v>
       </c>
@@ -6617,7 +6619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>234</v>
       </c>
@@ -6680,7 +6682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:27" ht="15.75" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>239</v>
       </c>
@@ -6743,7 +6745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:27" ht="15.75" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>244</v>
       </c>
@@ -6806,7 +6808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:27" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>248</v>
       </c>
@@ -6869,7 +6871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:27" ht="15.75" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>253</v>
       </c>
@@ -6932,7 +6934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:27" ht="15.75" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>257</v>
       </c>
@@ -6995,7 +6997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27" ht="15.75" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>262</v>
       </c>
@@ -7058,7 +7060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:27" ht="15.75" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>266</v>
       </c>
@@ -7121,7 +7123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:27" ht="15.75" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>271</v>
       </c>
@@ -7184,7 +7186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:27" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>276</v>
       </c>
@@ -7244,7 +7246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:27" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="s">
         <v>281</v>
       </c>
@@ -7307,7 +7309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:27" ht="15.75" customHeight="1">
       <c r="A47" s="1" t="s">
         <v>286</v>
       </c>
@@ -7374,7 +7376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:27" ht="15.75" customHeight="1">
       <c r="A48" s="1" t="s">
         <v>292</v>
       </c>
@@ -7437,7 +7439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:28" ht="15.75" customHeight="1">
       <c r="A49" s="1" t="s">
         <v>296</v>
       </c>
@@ -7500,7 +7502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:28" ht="15.75" customHeight="1">
       <c r="A50" s="1" t="s">
         <v>301</v>
       </c>
@@ -7563,7 +7565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:28" ht="15.75" customHeight="1">
       <c r="A51" s="1" t="s">
         <v>306</v>
       </c>
@@ -7626,7 +7628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:28" ht="15.75" customHeight="1">
       <c r="A52" s="1" t="s">
         <v>311</v>
       </c>
@@ -7689,7 +7691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:28" ht="15.75" customHeight="1">
       <c r="A53" s="1" t="s">
         <v>316</v>
       </c>
@@ -7756,7 +7758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:28" ht="15.75" customHeight="1">
       <c r="A54" s="1" t="s">
         <v>321</v>
       </c>
@@ -7821,7 +7823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:28" ht="15.75" customHeight="1">
       <c r="A55" s="1" t="s">
         <v>327</v>
       </c>
@@ -7884,7 +7886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:28" ht="15.75" customHeight="1">
       <c r="A56" s="1" t="s">
         <v>332</v>
       </c>
@@ -7947,7 +7949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:28" ht="15.75" customHeight="1">
       <c r="A57" s="1" t="s">
         <v>337</v>
       </c>
@@ -8010,7 +8012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:28" ht="15.75" customHeight="1">
       <c r="A58" s="1" t="s">
         <v>342</v>
       </c>
@@ -8077,7 +8079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:28" ht="15.75" customHeight="1">
       <c r="A59" s="1" t="s">
         <v>348</v>
       </c>
@@ -8136,7 +8138,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="60" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:28" ht="15.75" customHeight="1">
       <c r="A60" s="1" t="s">
         <v>354</v>
       </c>
@@ -8199,7 +8201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:28" ht="15.75" customHeight="1">
       <c r="A61" s="1" t="s">
         <v>358</v>
       </c>
@@ -8262,7 +8264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:28" ht="15.75" customHeight="1">
       <c r="A62" s="1" t="s">
         <v>362</v>
       </c>
@@ -8331,7 +8333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:28" ht="15.75" customHeight="1">
       <c r="A63" s="1" t="s">
         <v>368</v>
       </c>
@@ -8400,7 +8402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:28" ht="15.75" customHeight="1">
       <c r="A64" s="1" t="s">
         <v>374</v>
       </c>
@@ -8463,7 +8465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:28" ht="15.75" customHeight="1">
       <c r="A65" s="1" t="s">
         <v>379</v>
       </c>
@@ -8528,7 +8530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:28" ht="15.75" customHeight="1">
       <c r="A66" s="1" t="s">
         <v>383</v>
       </c>
@@ -8591,7 +8593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:28" ht="15.75" customHeight="1">
       <c r="A67" s="1" t="s">
         <v>389</v>
       </c>
@@ -8656,7 +8658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:28" ht="15.75" customHeight="1">
       <c r="A68" s="1" t="s">
         <v>393</v>
       </c>
@@ -8719,7 +8721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:28" ht="15.75" customHeight="1">
       <c r="A69" s="1" t="s">
         <v>397</v>
       </c>
@@ -8782,7 +8784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:28" ht="15.75" customHeight="1">
       <c r="A70" s="1" t="s">
         <v>401</v>
       </c>
@@ -8847,7 +8849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:28" ht="15.75" customHeight="1">
       <c r="A71" s="1" t="s">
         <v>405</v>
       </c>
@@ -8912,7 +8914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:28" ht="15.75" customHeight="1">
       <c r="A72" s="1" t="s">
         <v>412</v>
       </c>
@@ -8975,7 +8977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:28" ht="15.75" customHeight="1">
       <c r="A73" s="1" t="s">
         <v>416</v>
       </c>
@@ -9038,7 +9040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:28" ht="15.75" customHeight="1">
       <c r="A74" s="1" t="s">
         <v>421</v>
       </c>
@@ -9112,7 +9114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:28" ht="15.75" customHeight="1">
       <c r="A75" s="1" t="s">
         <v>428</v>
       </c>
@@ -9175,7 +9177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:28" ht="15.75" customHeight="1">
       <c r="A76" s="1" t="s">
         <v>433</v>
       </c>
@@ -9239,7 +9241,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:28" ht="15.75" customHeight="1">
       <c r="A77" s="1" t="s">
         <v>440</v>
       </c>
@@ -9302,7 +9304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:28" ht="15.75" customHeight="1">
       <c r="A78" s="1" t="s">
         <v>444</v>
       </c>
@@ -9365,7 +9367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:28" ht="15.75" customHeight="1">
       <c r="A79" s="1" t="s">
         <v>448</v>
       </c>
@@ -9428,7 +9430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:28" ht="15.75" customHeight="1">
       <c r="A80" s="1" t="s">
         <v>452</v>
       </c>
@@ -9491,7 +9493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:27" ht="15.75" customHeight="1">
       <c r="A81" s="1" t="s">
         <v>457</v>
       </c>
@@ -9554,7 +9556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:27" ht="15.75" customHeight="1">
       <c r="A82" s="1" t="s">
         <v>462</v>
       </c>
@@ -9628,7 +9630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:27" ht="15.75" customHeight="1">
       <c r="A83" s="1" t="s">
         <v>472</v>
       </c>
@@ -9691,7 +9693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:27" ht="15.75" customHeight="1">
       <c r="A84" s="1" t="s">
         <v>477</v>
       </c>
@@ -9764,7 +9766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:27" ht="15.75" customHeight="1">
       <c r="A85" s="1" t="s">
         <v>485</v>
       </c>
@@ -9827,7 +9829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:27" ht="15.75" customHeight="1">
       <c r="A86" s="1" t="s">
         <v>489</v>
       </c>
@@ -9890,7 +9892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:27" ht="15.75" customHeight="1">
       <c r="A87" s="1" t="s">
         <v>493</v>
       </c>
@@ -9953,7 +9955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:27" ht="15.75" customHeight="1">
       <c r="A88" s="1" t="s">
         <v>499</v>
       </c>
@@ -10016,7 +10018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:27" ht="15.75" customHeight="1">
       <c r="A89" s="1" t="s">
         <v>503</v>
       </c>
@@ -10079,7 +10081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:27" ht="15.75" customHeight="1">
       <c r="A90" s="1" t="s">
         <v>507</v>
       </c>
@@ -10149,7 +10151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:27" ht="15.75" customHeight="1">
       <c r="A91" s="1" t="s">
         <v>514</v>
       </c>
@@ -10212,7 +10214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:27" ht="15.75" customHeight="1">
       <c r="A92" s="1" t="s">
         <v>519</v>
       </c>
@@ -10277,7 +10279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:27" ht="15.75" customHeight="1">
       <c r="A93" s="1" t="s">
         <v>524</v>
       </c>
@@ -10344,7 +10346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:27" ht="15.75" customHeight="1">
       <c r="A94" s="1" t="s">
         <v>531</v>
       </c>
@@ -10409,7 +10411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:27" ht="15.75" customHeight="1">
       <c r="A95" s="1" t="s">
         <v>535</v>
       </c>
@@ -10472,7 +10474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:27" ht="15.75" customHeight="1">
       <c r="A96" s="1" t="s">
         <v>540</v>
       </c>
@@ -10535,7 +10537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:27" ht="15.75" customHeight="1">
       <c r="A97" s="1" t="s">
         <v>545</v>
       </c>
@@ -10600,7 +10602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:27" ht="15.75" customHeight="1">
       <c r="A98" s="1" t="s">
         <v>550</v>
       </c>
@@ -10663,7 +10665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:27" ht="15.75" customHeight="1">
       <c r="A99" s="1" t="s">
         <v>555</v>
       </c>
@@ -10726,7 +10728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:27" ht="15.75" customHeight="1">
       <c r="A100" s="1" t="s">
         <v>560</v>
       </c>
@@ -10791,7 +10793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:27" ht="15.75" customHeight="1">
       <c r="A101" s="1" t="s">
         <v>565</v>
       </c>
@@ -10854,7 +10856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:27" ht="15.75" customHeight="1">
       <c r="A102" s="1" t="s">
         <v>569</v>
       </c>
@@ -10917,7 +10919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:27" ht="15.75" customHeight="1">
       <c r="A103" s="1" t="s">
         <v>573</v>
       </c>
@@ -10980,7 +10982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:27" ht="15.75" customHeight="1">
       <c r="A104" s="1" t="s">
         <v>577</v>
       </c>
@@ -11043,7 +11045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:27" ht="15.75" customHeight="1">
       <c r="A105" s="1" t="s">
         <v>582</v>
       </c>
@@ -11106,7 +11108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:27" ht="15.75" customHeight="1">
       <c r="A106" s="1" t="s">
         <v>586</v>
       </c>
@@ -11169,7 +11171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:27" ht="15.75" customHeight="1">
       <c r="A107" s="1" t="s">
         <v>592</v>
       </c>
@@ -11232,7 +11234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:27" ht="15.75" customHeight="1">
       <c r="A108" s="1" t="s">
         <v>596</v>
       </c>
@@ -11297,7 +11299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:27" ht="15.75" customHeight="1">
       <c r="A109" s="1" t="s">
         <v>601</v>
       </c>
@@ -11362,7 +11364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:27" ht="15.75" customHeight="1">
       <c r="A110" s="1" t="s">
         <v>606</v>
       </c>
@@ -11425,7 +11427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:27" ht="15.75" customHeight="1">
       <c r="A111" s="1" t="s">
         <v>610</v>
       </c>
@@ -11491,7 +11493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:27" ht="15.75" customHeight="1">
       <c r="A112" s="1" t="s">
         <v>617</v>
       </c>
@@ -11556,7 +11558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:27" ht="15.75" customHeight="1">
       <c r="A113" s="1" t="s">
         <v>624</v>
       </c>
@@ -11619,7 +11621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:27" ht="15.75" customHeight="1">
       <c r="A114" s="1" t="s">
         <v>629</v>
       </c>
@@ -11682,7 +11684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:27" ht="15.75" customHeight="1">
       <c r="A115" s="1" t="s">
         <v>634</v>
       </c>
@@ -11747,7 +11749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:27" ht="15.75" customHeight="1">
       <c r="A116" s="1" t="s">
         <v>639</v>
       </c>
@@ -11810,7 +11812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:27" ht="15.75" customHeight="1">
       <c r="A117" s="1" t="s">
         <v>643</v>
       </c>
@@ -11873,7 +11875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:27" ht="15.75" customHeight="1">
       <c r="A118" s="1" t="s">
         <v>648</v>
       </c>
@@ -11936,7 +11938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:27" ht="15.75" customHeight="1">
       <c r="A119" s="1" t="s">
         <v>653</v>
       </c>
@@ -11999,7 +12001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:27" ht="15.75" customHeight="1">
       <c r="A120" s="1" t="s">
         <v>657</v>
       </c>
@@ -12062,7 +12064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:27" ht="15.75" customHeight="1">
       <c r="A121" s="1" t="s">
         <v>662</v>
       </c>
@@ -12127,7 +12129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:27" ht="15.75" customHeight="1">
       <c r="A122" s="1" t="s">
         <v>668</v>
       </c>
@@ -12190,7 +12192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:27" ht="15.75" customHeight="1">
       <c r="A123" s="1" t="s">
         <v>673</v>
       </c>
@@ -12253,7 +12255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:27" ht="15.75" customHeight="1">
       <c r="A124" s="1" t="s">
         <v>677</v>
       </c>
@@ -12316,7 +12318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:27" ht="15.75" customHeight="1">
       <c r="A125" s="1" t="s">
         <v>682</v>
       </c>
@@ -12379,7 +12381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:27" ht="15.75" customHeight="1">
       <c r="A126" s="1" t="s">
         <v>688</v>
       </c>
@@ -12445,7 +12447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:27" ht="15.75" customHeight="1">
       <c r="A127" s="1" t="s">
         <v>693</v>
       </c>
@@ -12510,7 +12512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:27" ht="15.75" customHeight="1">
       <c r="A128" s="1" t="s">
         <v>700</v>
       </c>
@@ -12575,7 +12577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:28" ht="15.75" customHeight="1">
       <c r="A129" s="1" t="s">
         <v>706</v>
       </c>
@@ -12638,7 +12640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:28" ht="15.75" customHeight="1">
       <c r="A130" s="1" t="s">
         <v>711</v>
       </c>
@@ -12703,7 +12705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:28" ht="15.75" customHeight="1">
       <c r="A131" s="1" t="s">
         <v>716</v>
       </c>
@@ -12768,7 +12770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:28" ht="15.75" customHeight="1">
       <c r="A132" s="1" t="s">
         <v>721</v>
       </c>
@@ -12831,7 +12833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:28" ht="15.75" customHeight="1">
       <c r="A133" s="1" t="s">
         <v>726</v>
       </c>
@@ -12894,7 +12896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:28" ht="15.75" customHeight="1">
       <c r="A134" s="1" t="s">
         <v>730</v>
       </c>
@@ -12957,7 +12959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:28" ht="15.75" customHeight="1">
       <c r="A135" s="1" t="s">
         <v>735</v>
       </c>
@@ -13022,7 +13024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:28" ht="15.75" customHeight="1">
       <c r="A136" s="1" t="s">
         <v>740</v>
       </c>
@@ -13085,7 +13087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:28" ht="15.75" customHeight="1">
       <c r="A137" s="1" t="s">
         <v>745</v>
       </c>
@@ -13148,7 +13150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:28" ht="15.75" customHeight="1">
       <c r="A138" s="1" t="s">
         <v>749</v>
       </c>
@@ -13214,7 +13216,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="139" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:28" ht="15.75" customHeight="1">
       <c r="A139" s="1" t="s">
         <v>756</v>
       </c>
@@ -13277,7 +13279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:28" ht="15.75" customHeight="1">
       <c r="A140" s="1" t="s">
         <v>761</v>
       </c>
@@ -13340,7 +13342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:28" ht="15.75" customHeight="1">
       <c r="A141" s="1" t="s">
         <v>765</v>
       </c>
@@ -13403,7 +13405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:28" ht="15.75" customHeight="1">
       <c r="A142" s="1" t="s">
         <v>770</v>
       </c>
@@ -13466,7 +13468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:28" ht="15.75" customHeight="1">
       <c r="A143" s="1" t="s">
         <v>775</v>
       </c>
@@ -13531,7 +13533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:28" ht="15.75" customHeight="1">
       <c r="A144" s="1" t="s">
         <v>780</v>
       </c>
@@ -13594,7 +13596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:27" ht="15.75" customHeight="1">
       <c r="A145" s="1" t="s">
         <v>785</v>
       </c>
@@ -13657,7 +13659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:27" ht="15.75" customHeight="1">
       <c r="A146" s="1" t="s">
         <v>791</v>
       </c>
@@ -13720,7 +13722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:27" ht="15.75" customHeight="1">
       <c r="A147" s="1" t="s">
         <v>795</v>
       </c>
@@ -13783,7 +13785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:27" ht="15.75" customHeight="1">
       <c r="A148" s="1" t="s">
         <v>799</v>
       </c>
@@ -13848,7 +13850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:27" ht="15.75" customHeight="1">
       <c r="A149" s="1" t="s">
         <v>805</v>
       </c>
@@ -13913,7 +13915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:27" ht="15.75" customHeight="1">
       <c r="A150" s="1" t="s">
         <v>810</v>
       </c>
@@ -13976,7 +13978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:27" ht="15.75" customHeight="1">
       <c r="A151" s="1" t="s">
         <v>815</v>
       </c>
@@ -14039,7 +14041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:27" ht="15.75" customHeight="1">
       <c r="A152" s="1" t="s">
         <v>820</v>
       </c>
@@ -14102,7 +14104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:27" ht="15.75" customHeight="1">
       <c r="A153" s="1" t="s">
         <v>825</v>
       </c>
@@ -14165,7 +14167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:27" ht="15.75" customHeight="1">
       <c r="A154" s="1" t="s">
         <v>830</v>
       </c>
@@ -14228,7 +14230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:27" ht="15.75" customHeight="1">
       <c r="A155" s="1" t="s">
         <v>834</v>
       </c>
@@ -14291,7 +14293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:27" ht="15.75" customHeight="1">
       <c r="A156" s="1" t="s">
         <v>838</v>
       </c>
@@ -14354,7 +14356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:27" ht="15.75" customHeight="1">
       <c r="A157" s="1" t="s">
         <v>843</v>
       </c>
@@ -14419,7 +14421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:27" ht="15.75" customHeight="1">
       <c r="A158" s="1" t="s">
         <v>848</v>
       </c>
@@ -14484,7 +14486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:27" ht="15.75" customHeight="1">
       <c r="A159" s="1" t="s">
         <v>853</v>
       </c>
@@ -14547,7 +14549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:27" ht="15.75" customHeight="1">
       <c r="A160" s="1" t="s">
         <v>857</v>
       </c>
@@ -14610,7 +14612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:28" ht="15.75" customHeight="1">
       <c r="A161" s="1" t="s">
         <v>862</v>
       </c>
@@ -14673,7 +14675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:28" ht="15.75" customHeight="1">
       <c r="A162" s="1" t="s">
         <v>867</v>
       </c>
@@ -14736,7 +14738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:28" ht="15.75" customHeight="1">
       <c r="A163" s="1" t="s">
         <v>871</v>
       </c>
@@ -14799,7 +14801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:28" ht="15.75" customHeight="1">
       <c r="A164" s="1" t="s">
         <v>876</v>
       </c>
@@ -14862,7 +14864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:28" ht="15.75" customHeight="1">
       <c r="A165" s="1" t="s">
         <v>881</v>
       </c>
@@ -14925,7 +14927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:28" ht="15.75" customHeight="1">
       <c r="A166" s="1" t="s">
         <v>886</v>
       </c>
@@ -14990,7 +14992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:28" ht="15.75" customHeight="1">
       <c r="A167" s="1" t="s">
         <v>891</v>
       </c>
@@ -15061,7 +15063,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="168" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:28" ht="15.75" customHeight="1">
       <c r="A168" s="1" t="s">
         <v>899</v>
       </c>
@@ -15124,7 +15126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:28" ht="15.75" customHeight="1">
       <c r="A169" s="1" t="s">
         <v>903</v>
       </c>
@@ -15189,7 +15191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:28" ht="15.75" customHeight="1">
       <c r="A170" s="1" t="s">
         <v>908</v>
       </c>
@@ -15252,7 +15254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:28" ht="15.75" customHeight="1">
       <c r="A171" s="1" t="s">
         <v>912</v>
       </c>
@@ -15315,7 +15317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:28" ht="15.75" customHeight="1">
       <c r="A172" s="1" t="s">
         <v>916</v>
       </c>
@@ -15378,7 +15380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:28" ht="15.75" customHeight="1">
       <c r="A173" s="1" t="s">
         <v>920</v>
       </c>
@@ -15441,7 +15443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:28" ht="15.75" customHeight="1">
       <c r="A174" s="1" t="s">
         <v>925</v>
       </c>
@@ -15504,7 +15506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:28" ht="15.75" customHeight="1">
       <c r="A175" s="1" t="s">
         <v>930</v>
       </c>
@@ -15569,7 +15571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:28" ht="15.75" customHeight="1">
       <c r="A176" s="1" t="s">
         <v>935</v>
       </c>
@@ -15632,7 +15634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:27" ht="15.75" customHeight="1">
       <c r="A177" s="1" t="s">
         <v>939</v>
       </c>
@@ -15698,7 +15700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:27" ht="15.75" customHeight="1">
       <c r="A178" s="1" t="s">
         <v>944</v>
       </c>
@@ -15761,7 +15763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:27" ht="15.75" customHeight="1">
       <c r="A179" s="1" t="s">
         <v>949</v>
       </c>
@@ -15829,7 +15831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:27" ht="15.75" customHeight="1">
       <c r="A180" s="1" t="s">
         <v>956</v>
       </c>
@@ -15892,7 +15894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:27" ht="15.75" customHeight="1">
       <c r="A181" s="1" t="s">
         <v>961</v>
       </c>
@@ -15955,7 +15957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:27" ht="15.75" customHeight="1">
       <c r="A182" s="1" t="s">
         <v>967</v>
       </c>
@@ -16020,7 +16022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:27" ht="15.75" customHeight="1">
       <c r="A183" s="1" t="s">
         <v>972</v>
       </c>
@@ -16085,7 +16087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:27" ht="15.75" customHeight="1">
       <c r="A184" s="1" t="s">
         <v>978</v>
       </c>
@@ -16148,7 +16150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:27" ht="15.75" customHeight="1">
       <c r="A185" s="1" t="s">
         <v>983</v>
       </c>
@@ -16211,7 +16213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:27" ht="15.75" customHeight="1">
       <c r="A186" s="1" t="s">
         <v>988</v>
       </c>
@@ -16282,7 +16284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:27" ht="15.75" customHeight="1">
       <c r="A187" s="1" t="s">
         <v>996</v>
       </c>
@@ -16350,7 +16352,7 @@
         <v xml:space="preserve">FALSE </v>
       </c>
     </row>
-    <row r="188" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:27" ht="15.75" customHeight="1">
       <c r="A188" s="1" t="s">
         <v>1003</v>
       </c>
@@ -16418,7 +16420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:27" ht="15.75" customHeight="1">
       <c r="A189" s="1" t="s">
         <v>1008</v>
       </c>
@@ -16481,7 +16483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:27" ht="15.75" customHeight="1">
       <c r="A190" s="1" t="s">
         <v>1013</v>
       </c>
@@ -16544,7 +16546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:27" ht="15.75" customHeight="1">
       <c r="A191" s="1" t="s">
         <v>1018</v>
       </c>
@@ -16607,7 +16609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:27" ht="15.75" customHeight="1">
       <c r="A192" s="1" t="s">
         <v>1023</v>
       </c>
@@ -16672,7 +16674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:28" ht="15.75" customHeight="1">
       <c r="A193" s="1" t="s">
         <v>1028</v>
       </c>
@@ -16740,7 +16742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:28" ht="15.75" customHeight="1">
       <c r="A194" s="1" t="s">
         <v>1034</v>
       </c>
@@ -16803,7 +16805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:28" ht="15.75" customHeight="1">
       <c r="A195" s="7" t="s">
         <v>1039</v>
       </c>
@@ -16869,7 +16871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:28" ht="15.75" customHeight="1">
       <c r="A196" s="7" t="s">
         <v>1044</v>
       </c>
@@ -16939,7 +16941,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="197" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:28" ht="15.75" customHeight="1">
       <c r="A197" s="7" t="s">
         <v>1049</v>
       </c>
@@ -17005,7 +17007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:28" ht="15.75" customHeight="1">
       <c r="A198" s="7" t="s">
         <v>1053</v>
       </c>
@@ -17071,7 +17073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:28" ht="15.75" customHeight="1">
       <c r="A199" s="7" t="s">
         <v>1057</v>
       </c>
@@ -17137,7 +17139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:28" ht="15.75" customHeight="1">
       <c r="A200" s="7" t="s">
         <v>1062</v>
       </c>
@@ -17203,7 +17205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:28" ht="15.75" customHeight="1">
       <c r="A201" s="7" t="s">
         <v>1067</v>
       </c>
@@ -17269,7 +17271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:28" ht="15.75" customHeight="1">
       <c r="A202" s="1" t="s">
         <v>1071</v>
       </c>
@@ -17330,7 +17332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:28" ht="15.75" customHeight="1">
       <c r="A203" s="1" t="s">
         <v>1076</v>
       </c>
@@ -17391,7 +17393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:28" ht="15.75" customHeight="1">
       <c r="A204" s="1" t="s">
         <v>1080</v>
       </c>
@@ -17452,7 +17454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:28" ht="15.75" customHeight="1">
       <c r="A205" s="1" t="s">
         <v>1084</v>
       </c>
@@ -17513,7 +17515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:28" ht="15.75" customHeight="1">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -17537,7 +17539,7 @@
       <c r="U206" s="3"/>
       <c r="AA206" s="1"/>
     </row>
-    <row r="207" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:28" ht="15.75" customHeight="1">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -17561,7 +17563,7 @@
       <c r="U207" s="3"/>
       <c r="AA207" s="1"/>
     </row>
-    <row r="208" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:28" ht="15.75" customHeight="1">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -17585,7 +17587,7 @@
       <c r="U208" s="3"/>
       <c r="AA208" s="1"/>
     </row>
-    <row r="209" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:27" ht="15.75" customHeight="1">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -17609,7 +17611,7 @@
       <c r="U209" s="3"/>
       <c r="AA209" s="1"/>
     </row>
-    <row r="210" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:27" ht="15.75" customHeight="1">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -17633,7 +17635,7 @@
       <c r="U210" s="3"/>
       <c r="AA210" s="1"/>
     </row>
-    <row r="211" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:27" ht="15.75" customHeight="1">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -17657,7 +17659,7 @@
       <c r="U211" s="3"/>
       <c r="AA211" s="1"/>
     </row>
-    <row r="212" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:27" ht="15.75" customHeight="1">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -17681,7 +17683,7 @@
       <c r="U212" s="3"/>
       <c r="AA212" s="1"/>
     </row>
-    <row r="213" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:27" ht="15.75" customHeight="1">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -17705,7 +17707,7 @@
       <c r="U213" s="3"/>
       <c r="AA213" s="1"/>
     </row>
-    <row r="214" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:27" ht="15.75" customHeight="1">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -17729,7 +17731,7 @@
       <c r="U214" s="3"/>
       <c r="AA214" s="1"/>
     </row>
-    <row r="215" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:27" ht="15.75" customHeight="1">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -17753,7 +17755,7 @@
       <c r="U215" s="3"/>
       <c r="AA215" s="1"/>
     </row>
-    <row r="216" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:27" ht="15.75" customHeight="1">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -17777,7 +17779,7 @@
       <c r="U216" s="3"/>
       <c r="AA216" s="1"/>
     </row>
-    <row r="217" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:27" ht="15.75" customHeight="1">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -17801,7 +17803,7 @@
       <c r="U217" s="3"/>
       <c r="AA217" s="1"/>
     </row>
-    <row r="218" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:27" ht="15.75" customHeight="1">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -17825,7 +17827,7 @@
       <c r="U218" s="3"/>
       <c r="AA218" s="1"/>
     </row>
-    <row r="219" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:27" ht="15.75" customHeight="1">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -17849,7 +17851,7 @@
       <c r="U219" s="3"/>
       <c r="AA219" s="1"/>
     </row>
-    <row r="220" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:27" ht="15.75" customHeight="1">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -17873,7 +17875,7 @@
       <c r="U220" s="3"/>
       <c r="AA220" s="1"/>
     </row>
-    <row r="221" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:27" ht="15.75" customHeight="1">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -17897,7 +17899,7 @@
       <c r="U221" s="3"/>
       <c r="AA221" s="1"/>
     </row>
-    <row r="222" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:27" ht="15.75" customHeight="1">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -17921,7 +17923,7 @@
       <c r="U222" s="3"/>
       <c r="AA222" s="1"/>
     </row>
-    <row r="223" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:27" ht="15.75" customHeight="1">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -17945,7 +17947,7 @@
       <c r="U223" s="3"/>
       <c r="AA223" s="1"/>
     </row>
-    <row r="224" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:27" ht="15.75" customHeight="1">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -17969,7 +17971,7 @@
       <c r="U224" s="3"/>
       <c r="AA224" s="1"/>
     </row>
-    <row r="225" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:27" ht="15.75" customHeight="1">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -17993,7 +17995,7 @@
       <c r="U225" s="3"/>
       <c r="AA225" s="1"/>
     </row>
-    <row r="226" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:27" ht="15.75" customHeight="1">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -18017,7 +18019,7 @@
       <c r="U226" s="3"/>
       <c r="AA226" s="1"/>
     </row>
-    <row r="227" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:27" ht="15.75" customHeight="1">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -18041,7 +18043,7 @@
       <c r="U227" s="3"/>
       <c r="AA227" s="1"/>
     </row>
-    <row r="228" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:27" ht="15.75" customHeight="1">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -18065,7 +18067,7 @@
       <c r="U228" s="3"/>
       <c r="AA228" s="1"/>
     </row>
-    <row r="229" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:27" ht="15.75" customHeight="1">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -18089,7 +18091,7 @@
       <c r="U229" s="3"/>
       <c r="AA229" s="1"/>
     </row>
-    <row r="230" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:27" ht="15.75" customHeight="1">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -18113,7 +18115,7 @@
       <c r="U230" s="3"/>
       <c r="AA230" s="1"/>
     </row>
-    <row r="231" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:27" ht="15.75" customHeight="1">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -18137,7 +18139,7 @@
       <c r="U231" s="3"/>
       <c r="AA231" s="1"/>
     </row>
-    <row r="232" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:27" ht="15.75" customHeight="1">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -18161,7 +18163,7 @@
       <c r="U232" s="3"/>
       <c r="AA232" s="1"/>
     </row>
-    <row r="233" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:27" ht="15.75" customHeight="1">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -18185,7 +18187,7 @@
       <c r="U233" s="3"/>
       <c r="AA233" s="1"/>
     </row>
-    <row r="234" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:27" ht="15.75" customHeight="1">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -18209,7 +18211,7 @@
       <c r="U234" s="3"/>
       <c r="AA234" s="1"/>
     </row>
-    <row r="235" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:27" ht="15.75" customHeight="1">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -18233,7 +18235,7 @@
       <c r="U235" s="3"/>
       <c r="AA235" s="1"/>
     </row>
-    <row r="236" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:27" ht="15.75" customHeight="1">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -18257,7 +18259,7 @@
       <c r="U236" s="3"/>
       <c r="AA236" s="1"/>
     </row>
-    <row r="237" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:27" ht="15.75" customHeight="1">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -18281,7 +18283,7 @@
       <c r="U237" s="3"/>
       <c r="AA237" s="1"/>
     </row>
-    <row r="238" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:27" ht="15.75" customHeight="1">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -18305,7 +18307,7 @@
       <c r="U238" s="3"/>
       <c r="AA238" s="1"/>
     </row>
-    <row r="239" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:27" ht="15.75" customHeight="1">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -18329,7 +18331,7 @@
       <c r="U239" s="3"/>
       <c r="AA239" s="1"/>
     </row>
-    <row r="240" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:27" ht="15.75" customHeight="1">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -18353,7 +18355,7 @@
       <c r="U240" s="3"/>
       <c r="AA240" s="1"/>
     </row>
-    <row r="241" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:27" ht="15.75" customHeight="1">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -18377,7 +18379,7 @@
       <c r="U241" s="3"/>
       <c r="AA241" s="1"/>
     </row>
-    <row r="242" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:27" ht="15.75" customHeight="1">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -18401,7 +18403,7 @@
       <c r="U242" s="3"/>
       <c r="AA242" s="1"/>
     </row>
-    <row r="243" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:27" ht="15.75" customHeight="1">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -18425,7 +18427,7 @@
       <c r="U243" s="3"/>
       <c r="AA243" s="1"/>
     </row>
-    <row r="244" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:27" ht="15.75" customHeight="1">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -18449,7 +18451,7 @@
       <c r="U244" s="3"/>
       <c r="AA244" s="1"/>
     </row>
-    <row r="245" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:27" ht="15.75" customHeight="1">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -18473,7 +18475,7 @@
       <c r="U245" s="3"/>
       <c r="AA245" s="1"/>
     </row>
-    <row r="246" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:27" ht="15.75" customHeight="1">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -18497,7 +18499,7 @@
       <c r="U246" s="3"/>
       <c r="AA246" s="1"/>
     </row>
-    <row r="247" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:27" ht="15.75" customHeight="1">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -18521,7 +18523,7 @@
       <c r="U247" s="3"/>
       <c r="AA247" s="1"/>
     </row>
-    <row r="248" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:27" ht="15.75" customHeight="1">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -18545,7 +18547,7 @@
       <c r="U248" s="3"/>
       <c r="AA248" s="1"/>
     </row>
-    <row r="249" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:27" ht="15.75" customHeight="1">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -18569,7 +18571,7 @@
       <c r="U249" s="3"/>
       <c r="AA249" s="1"/>
     </row>
-    <row r="250" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:27" ht="15.75" customHeight="1">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -18593,7 +18595,7 @@
       <c r="U250" s="3"/>
       <c r="AA250" s="1"/>
     </row>
-    <row r="251" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:27" ht="15.75" customHeight="1">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -18617,7 +18619,7 @@
       <c r="U251" s="3"/>
       <c r="AA251" s="1"/>
     </row>
-    <row r="252" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:27" ht="15.75" customHeight="1">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -18641,7 +18643,7 @@
       <c r="U252" s="3"/>
       <c r="AA252" s="1"/>
     </row>
-    <row r="253" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:27" ht="15.75" customHeight="1">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -18665,7 +18667,7 @@
       <c r="U253" s="3"/>
       <c r="AA253" s="1"/>
     </row>
-    <row r="254" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:27" ht="15.75" customHeight="1">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -18689,7 +18691,7 @@
       <c r="U254" s="3"/>
       <c r="AA254" s="1"/>
     </row>
-    <row r="255" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:27" ht="15.75" customHeight="1">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -18713,7 +18715,7 @@
       <c r="U255" s="3"/>
       <c r="AA255" s="1"/>
     </row>
-    <row r="256" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:27" ht="15.75" customHeight="1">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -18737,7 +18739,7 @@
       <c r="U256" s="3"/>
       <c r="AA256" s="1"/>
     </row>
-    <row r="257" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:27" ht="15.75" customHeight="1">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -18761,7 +18763,7 @@
       <c r="U257" s="3"/>
       <c r="AA257" s="1"/>
     </row>
-    <row r="258" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:27" ht="15.75" customHeight="1">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -18785,7 +18787,7 @@
       <c r="U258" s="3"/>
       <c r="AA258" s="1"/>
     </row>
-    <row r="259" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:27" ht="15.75" customHeight="1">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -18809,7 +18811,7 @@
       <c r="U259" s="3"/>
       <c r="AA259" s="1"/>
     </row>
-    <row r="260" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:27" ht="15.75" customHeight="1">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -18833,7 +18835,7 @@
       <c r="U260" s="3"/>
       <c r="AA260" s="1"/>
     </row>
-    <row r="261" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:27" ht="15.75" customHeight="1">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -18857,7 +18859,7 @@
       <c r="U261" s="3"/>
       <c r="AA261" s="1"/>
     </row>
-    <row r="262" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:27" ht="15.75" customHeight="1">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -18881,7 +18883,7 @@
       <c r="U262" s="3"/>
       <c r="AA262" s="1"/>
     </row>
-    <row r="263" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:27" ht="15.75" customHeight="1">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -18905,7 +18907,7 @@
       <c r="U263" s="3"/>
       <c r="AA263" s="1"/>
     </row>
-    <row r="264" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:27" ht="15.75" customHeight="1">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -18929,7 +18931,7 @@
       <c r="U264" s="3"/>
       <c r="AA264" s="1"/>
     </row>
-    <row r="265" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:27" ht="15.75" customHeight="1">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -18953,7 +18955,7 @@
       <c r="U265" s="3"/>
       <c r="AA265" s="1"/>
     </row>
-    <row r="266" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:27" ht="15.75" customHeight="1">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -18977,7 +18979,7 @@
       <c r="U266" s="3"/>
       <c r="AA266" s="1"/>
     </row>
-    <row r="267" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:27" ht="15.75" customHeight="1">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -19001,7 +19003,7 @@
       <c r="U267" s="3"/>
       <c r="AA267" s="1"/>
     </row>
-    <row r="268" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:27" ht="15.75" customHeight="1">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -19025,7 +19027,7 @@
       <c r="U268" s="3"/>
       <c r="AA268" s="1"/>
     </row>
-    <row r="269" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:27" ht="15.75" customHeight="1">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -19049,7 +19051,7 @@
       <c r="U269" s="3"/>
       <c r="AA269" s="1"/>
     </row>
-    <row r="270" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:27" ht="15.75" customHeight="1">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -19073,7 +19075,7 @@
       <c r="U270" s="3"/>
       <c r="AA270" s="1"/>
     </row>
-    <row r="271" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:27" ht="15.75" customHeight="1">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -19097,7 +19099,7 @@
       <c r="U271" s="3"/>
       <c r="AA271" s="1"/>
     </row>
-    <row r="272" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:27" ht="15.75" customHeight="1">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -19121,7 +19123,7 @@
       <c r="U272" s="3"/>
       <c r="AA272" s="1"/>
     </row>
-    <row r="273" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:27" ht="15.75" customHeight="1">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -19145,7 +19147,7 @@
       <c r="U273" s="3"/>
       <c r="AA273" s="1"/>
     </row>
-    <row r="274" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:27" ht="15.75" customHeight="1">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -19169,7 +19171,7 @@
       <c r="U274" s="3"/>
       <c r="AA274" s="1"/>
     </row>
-    <row r="275" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:27" ht="15.75" customHeight="1">
       <c r="A275" s="1" t="s">
         <v>1089</v>
       </c>
@@ -19201,7 +19203,7 @@
       <c r="U275" s="3"/>
       <c r="AA275" s="1"/>
     </row>
-    <row r="276" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:27" ht="15.75" customHeight="1">
       <c r="A276" s="1" t="s">
         <v>1090</v>
       </c>
@@ -19233,7 +19235,7 @@
       <c r="U276" s="3"/>
       <c r="AA276" s="1"/>
     </row>
-    <row r="277" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:27" ht="15.75" customHeight="1">
       <c r="A277" s="1" t="s">
         <v>1091</v>
       </c>
@@ -19265,7 +19267,7 @@
       <c r="U277" s="3"/>
       <c r="AA277" s="1"/>
     </row>
-    <row r="278" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:27" ht="15.75" customHeight="1">
       <c r="A278" s="1" t="s">
         <v>1092</v>
       </c>
@@ -19297,7 +19299,7 @@
       <c r="U278" s="3"/>
       <c r="AA278" s="1"/>
     </row>
-    <row r="279" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:27" ht="15.75" customHeight="1">
       <c r="A279" s="1" t="s">
         <v>1093</v>
       </c>
@@ -19329,7 +19331,7 @@
       <c r="U279" s="3"/>
       <c r="AA279" s="1"/>
     </row>
-    <row r="280" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:27" ht="15.75" customHeight="1">
       <c r="A280" s="1" t="s">
         <v>1094</v>
       </c>
@@ -19361,7 +19363,7 @@
       <c r="U280" s="3"/>
       <c r="AA280" s="1"/>
     </row>
-    <row r="281" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:27" ht="15.75" customHeight="1">
       <c r="A281" s="1" t="s">
         <v>1095</v>
       </c>
@@ -19393,7 +19395,7 @@
       <c r="U281" s="3"/>
       <c r="AA281" s="1"/>
     </row>
-    <row r="282" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:27" ht="15.75" customHeight="1">
       <c r="A282" s="1" t="s">
         <v>1096</v>
       </c>
@@ -19425,7 +19427,7 @@
       <c r="U282" s="3"/>
       <c r="AA282" s="1"/>
     </row>
-    <row r="283" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:27" ht="15.75" customHeight="1">
       <c r="A283" s="1" t="s">
         <v>1097</v>
       </c>
@@ -19457,7 +19459,7 @@
       <c r="U283" s="3"/>
       <c r="AA283" s="1"/>
     </row>
-    <row r="284" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:27" ht="15.75" customHeight="1">
       <c r="A284" s="1" t="s">
         <v>1098</v>
       </c>
@@ -19489,7 +19491,7 @@
       <c r="U284" s="3"/>
       <c r="AA284" s="1"/>
     </row>
-    <row r="285" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:27" ht="15.75" customHeight="1">
       <c r="A285" s="1" t="s">
         <v>1099</v>
       </c>
@@ -19521,7 +19523,7 @@
       <c r="U285" s="3"/>
       <c r="AA285" s="1"/>
     </row>
-    <row r="286" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:27" ht="15.75" customHeight="1">
       <c r="A286" s="1" t="s">
         <v>1100</v>
       </c>
@@ -19553,7 +19555,7 @@
       <c r="U286" s="3"/>
       <c r="AA286" s="1"/>
     </row>
-    <row r="287" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:27" ht="15.75" customHeight="1">
       <c r="A287" s="1" t="s">
         <v>1101</v>
       </c>
@@ -19585,7 +19587,7 @@
       <c r="U287" s="3"/>
       <c r="AA287" s="1"/>
     </row>
-    <row r="288" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:27" ht="15.75" customHeight="1">
       <c r="A288" s="1" t="s">
         <v>1102</v>
       </c>
@@ -19617,7 +19619,7 @@
       <c r="U288" s="3"/>
       <c r="AA288" s="1"/>
     </row>
-    <row r="289" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:27" ht="15.75" customHeight="1">
       <c r="A289" s="1" t="s">
         <v>1103</v>
       </c>
@@ -19649,7 +19651,7 @@
       <c r="U289" s="3"/>
       <c r="AA289" s="1"/>
     </row>
-    <row r="290" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:27" ht="15.75" customHeight="1">
       <c r="A290" s="1" t="s">
         <v>1104</v>
       </c>
@@ -19681,7 +19683,7 @@
       <c r="U290" s="3"/>
       <c r="AA290" s="1"/>
     </row>
-    <row r="291" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:27" ht="15.75" customHeight="1">
       <c r="A291" s="1" t="s">
         <v>1105</v>
       </c>
@@ -19713,7 +19715,7 @@
       <c r="U291" s="3"/>
       <c r="AA291" s="1"/>
     </row>
-    <row r="292" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:27" ht="15.75" customHeight="1">
       <c r="A292" s="1" t="s">
         <v>1106</v>
       </c>
@@ -19745,7 +19747,7 @@
       <c r="U292" s="3"/>
       <c r="AA292" s="1"/>
     </row>
-    <row r="293" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:27" ht="15.75" customHeight="1">
       <c r="A293" s="1" t="s">
         <v>1107</v>
       </c>
@@ -19777,7 +19779,7 @@
       <c r="U293" s="3"/>
       <c r="AA293" s="1"/>
     </row>
-    <row r="294" spans="1:27" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:27" ht="170.1" customHeight="1">
       <c r="A294" s="1" t="s">
         <v>1108</v>
       </c>
@@ -19809,7 +19811,7 @@
       <c r="U294" s="3"/>
       <c r="AA294" s="1"/>
     </row>
-    <row r="295" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:27" ht="15.75" customHeight="1">
       <c r="A295" s="1" t="s">
         <v>1109</v>
       </c>
@@ -19841,7 +19843,7 @@
       <c r="U295" s="3"/>
       <c r="AA295" s="1"/>
     </row>
-    <row r="296" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:27" ht="15.75" customHeight="1">
       <c r="A296" s="1" t="s">
         <v>1110</v>
       </c>
@@ -19873,7 +19875,7 @@
       <c r="U296" s="3"/>
       <c r="AA296" s="1"/>
     </row>
-    <row r="297" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:27" ht="15.75" customHeight="1">
       <c r="A297" s="1" t="s">
         <v>1111</v>
       </c>
@@ -19905,7 +19907,7 @@
       <c r="U297" s="3"/>
       <c r="AA297" s="1"/>
     </row>
-    <row r="298" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:27" ht="15.75" customHeight="1">
       <c r="A298" s="1" t="s">
         <v>1112</v>
       </c>
@@ -19937,7 +19939,7 @@
       <c r="U298" s="3"/>
       <c r="AA298" s="1"/>
     </row>
-    <row r="299" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:27" ht="15.75" customHeight="1">
       <c r="A299" s="1" t="s">
         <v>1113</v>
       </c>
@@ -19969,7 +19971,7 @@
       <c r="U299" s="3"/>
       <c r="AA299" s="1"/>
     </row>
-    <row r="300" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:27" ht="15.75" customHeight="1">
       <c r="A300" s="1" t="s">
         <v>1114</v>
       </c>
@@ -20001,7 +20003,7 @@
       <c r="U300" s="3"/>
       <c r="AA300" s="1"/>
     </row>
-    <row r="301" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:27" ht="15.75" customHeight="1">
       <c r="A301" s="1" t="s">
         <v>1115</v>
       </c>
@@ -20033,7 +20035,7 @@
       <c r="U301" s="3"/>
       <c r="AA301" s="1"/>
     </row>
-    <row r="302" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:27" ht="15.75" customHeight="1">
       <c r="A302" s="1" t="s">
         <v>1116</v>
       </c>
@@ -20065,7 +20067,7 @@
       <c r="U302" s="3"/>
       <c r="AA302" s="1"/>
     </row>
-    <row r="303" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:27" ht="15.75" customHeight="1">
       <c r="A303" s="1" t="s">
         <v>1117</v>
       </c>
@@ -20097,7 +20099,7 @@
       <c r="U303" s="3"/>
       <c r="AA303" s="1"/>
     </row>
-    <row r="304" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:27" ht="15.75" customHeight="1">
       <c r="A304" s="1" t="s">
         <v>1118</v>
       </c>
@@ -20129,7 +20131,7 @@
       <c r="U304" s="3"/>
       <c r="AA304" s="1"/>
     </row>
-    <row r="305" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:27" ht="15.75" customHeight="1">
       <c r="A305" s="1" t="s">
         <v>1119</v>
       </c>
@@ -20161,7 +20163,7 @@
       <c r="U305" s="3"/>
       <c r="AA305" s="1"/>
     </row>
-    <row r="306" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:27" ht="15.75" customHeight="1">
       <c r="A306" s="1" t="s">
         <v>1120</v>
       </c>
@@ -20193,7 +20195,7 @@
       <c r="U306" s="3"/>
       <c r="AA306" s="1"/>
     </row>
-    <row r="307" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:27" ht="15.75" customHeight="1">
       <c r="A307" s="1" t="s">
         <v>1121</v>
       </c>
@@ -20225,7 +20227,7 @@
       <c r="U307" s="3"/>
       <c r="AA307" s="1"/>
     </row>
-    <row r="308" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:27" ht="15.75" customHeight="1">
       <c r="A308" s="1" t="s">
         <v>1122</v>
       </c>
@@ -20257,7 +20259,7 @@
       <c r="U308" s="3"/>
       <c r="AA308" s="1"/>
     </row>
-    <row r="309" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:27" ht="15.75" customHeight="1">
       <c r="A309" s="1" t="s">
         <v>1123</v>
       </c>
@@ -20289,7 +20291,7 @@
       <c r="U309" s="3"/>
       <c r="AA309" s="1"/>
     </row>
-    <row r="310" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:27" ht="15.75" customHeight="1">
       <c r="A310" s="1" t="s">
         <v>1124</v>
       </c>
@@ -20321,7 +20323,7 @@
       <c r="U310" s="3"/>
       <c r="AA310" s="1"/>
     </row>
-    <row r="311" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:27" ht="15.75" customHeight="1">
       <c r="A311" s="1" t="s">
         <v>1125</v>
       </c>
@@ -20353,7 +20355,7 @@
       <c r="U311" s="3"/>
       <c r="AA311" s="1"/>
     </row>
-    <row r="312" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:27" ht="15.75" customHeight="1">
       <c r="A312" s="1" t="s">
         <v>1126</v>
       </c>
@@ -20385,7 +20387,7 @@
       <c r="U312" s="3"/>
       <c r="AA312" s="1"/>
     </row>
-    <row r="313" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:27" ht="15.75" customHeight="1">
       <c r="A313" s="1" t="s">
         <v>1127</v>
       </c>
@@ -20417,7 +20419,7 @@
       <c r="U313" s="3"/>
       <c r="AA313" s="1"/>
     </row>
-    <row r="314" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:27" ht="15.75" customHeight="1">
       <c r="A314" s="1" t="s">
         <v>1128</v>
       </c>
@@ -20449,7 +20451,7 @@
       <c r="U314" s="3"/>
       <c r="AA314" s="1"/>
     </row>
-    <row r="315" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:27" ht="15.75" customHeight="1">
       <c r="A315" s="1" t="s">
         <v>1129</v>
       </c>
@@ -20481,7 +20483,7 @@
       <c r="U315" s="3"/>
       <c r="AA315" s="1"/>
     </row>
-    <row r="316" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:27" ht="15.75" customHeight="1">
       <c r="A316" s="1" t="s">
         <v>1131</v>
       </c>
@@ -20513,7 +20515,7 @@
       <c r="U316" s="3"/>
       <c r="AA316" s="1"/>
     </row>
-    <row r="317" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:27" ht="15.75" customHeight="1">
       <c r="A317" s="1" t="s">
         <v>1132</v>
       </c>
@@ -20545,7 +20547,7 @@
       <c r="U317" s="3"/>
       <c r="AA317" s="1"/>
     </row>
-    <row r="318" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:27" ht="15.75" customHeight="1">
       <c r="A318" s="1" t="s">
         <v>1133</v>
       </c>
@@ -20577,7 +20579,7 @@
       <c r="U318" s="3"/>
       <c r="AA318" s="1"/>
     </row>
-    <row r="319" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:27" ht="15.75" customHeight="1">
       <c r="A319" s="1" t="s">
         <v>1134</v>
       </c>
@@ -20609,7 +20611,7 @@
       <c r="U319" s="3"/>
       <c r="AA319" s="1"/>
     </row>
-    <row r="320" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:27" ht="15.75" customHeight="1">
       <c r="A320" s="1" t="s">
         <v>1135</v>
       </c>
@@ -20641,7 +20643,7 @@
       <c r="U320" s="3"/>
       <c r="AA320" s="1"/>
     </row>
-    <row r="321" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:27" ht="15.75" customHeight="1">
       <c r="A321" s="1" t="s">
         <v>1136</v>
       </c>
@@ -20673,7 +20675,7 @@
       <c r="U321" s="3"/>
       <c r="AA321" s="1"/>
     </row>
-    <row r="322" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:27" ht="15.75" customHeight="1">
       <c r="A322" s="1" t="s">
         <v>1137</v>
       </c>
@@ -20705,7 +20707,7 @@
       <c r="U322" s="3"/>
       <c r="AA322" s="1"/>
     </row>
-    <row r="323" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:27" ht="15.75" customHeight="1">
       <c r="A323" s="1" t="s">
         <v>1138</v>
       </c>
@@ -20737,7 +20739,7 @@
       <c r="U323" s="3"/>
       <c r="AA323" s="1"/>
     </row>
-    <row r="324" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:27" ht="15.75" customHeight="1">
       <c r="A324" s="1" t="s">
         <v>1139</v>
       </c>
@@ -20769,7 +20771,7 @@
       <c r="U324" s="3"/>
       <c r="AA324" s="1"/>
     </row>
-    <row r="325" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:27" ht="15.75" customHeight="1">
       <c r="A325" s="1" t="s">
         <v>1140</v>
       </c>
@@ -20801,7 +20803,7 @@
       <c r="U325" s="3"/>
       <c r="AA325" s="1"/>
     </row>
-    <row r="326" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:27" ht="15.75" customHeight="1">
       <c r="A326" s="1" t="s">
         <v>1141</v>
       </c>
@@ -20833,7 +20835,7 @@
       <c r="U326" s="3"/>
       <c r="AA326" s="1"/>
     </row>
-    <row r="327" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:27" ht="15.75" customHeight="1">
       <c r="A327" s="1" t="s">
         <v>1143</v>
       </c>
@@ -20865,7 +20867,7 @@
       <c r="U327" s="3"/>
       <c r="AA327" s="1"/>
     </row>
-    <row r="328" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:27" ht="15.75" customHeight="1">
       <c r="A328" s="1" t="s">
         <v>1144</v>
       </c>
@@ -20897,7 +20899,7 @@
       <c r="U328" s="3"/>
       <c r="AA328" s="1"/>
     </row>
-    <row r="329" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:27" ht="15.75" customHeight="1">
       <c r="A329" s="1" t="s">
         <v>1145</v>
       </c>
@@ -20929,7 +20931,7 @@
       <c r="U329" s="3"/>
       <c r="AA329" s="1"/>
     </row>
-    <row r="330" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:27" ht="15.75" customHeight="1">
       <c r="A330" s="1" t="s">
         <v>1146</v>
       </c>
@@ -20961,7 +20963,7 @@
       <c r="U330" s="3"/>
       <c r="AA330" s="1"/>
     </row>
-    <row r="331" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:27" ht="15.75" customHeight="1">
       <c r="A331" s="1" t="s">
         <v>1147</v>
       </c>
@@ -20993,7 +20995,7 @@
       <c r="U331" s="3"/>
       <c r="AA331" s="1"/>
     </row>
-    <row r="332" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:27" ht="15.75" customHeight="1">
       <c r="A332" s="1" t="s">
         <v>1148</v>
       </c>
@@ -21025,7 +21027,7 @@
       <c r="U332" s="3"/>
       <c r="AA332" s="1"/>
     </row>
-    <row r="333" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:27" ht="15.75" customHeight="1">
       <c r="A333" s="1" t="s">
         <v>1149</v>
       </c>
@@ -21057,7 +21059,7 @@
       <c r="U333" s="3"/>
       <c r="AA333" s="1"/>
     </row>
-    <row r="334" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:27" ht="15.75" customHeight="1">
       <c r="A334" s="1" t="s">
         <v>1150</v>
       </c>
@@ -21089,7 +21091,7 @@
       <c r="U334" s="3"/>
       <c r="AA334" s="1"/>
     </row>
-    <row r="335" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:27" ht="15.75" customHeight="1">
       <c r="A335" s="1" t="s">
         <v>1151</v>
       </c>
@@ -21121,7 +21123,7 @@
       <c r="U335" s="3"/>
       <c r="AA335" s="1"/>
     </row>
-    <row r="336" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:27" ht="15.75" customHeight="1">
       <c r="A336" s="1" t="s">
         <v>1152</v>
       </c>
@@ -21153,7 +21155,7 @@
       <c r="U336" s="3"/>
       <c r="AA336" s="1"/>
     </row>
-    <row r="337" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:27" ht="15.75" customHeight="1">
       <c r="A337" s="1" t="s">
         <v>1153</v>
       </c>
@@ -21185,7 +21187,7 @@
       <c r="U337" s="3"/>
       <c r="AA337" s="1"/>
     </row>
-    <row r="338" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:27" ht="15.75" customHeight="1">
       <c r="A338" s="1" t="s">
         <v>1155</v>
       </c>
@@ -21217,7 +21219,7 @@
       <c r="U338" s="3"/>
       <c r="AA338" s="1"/>
     </row>
-    <row r="339" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:27" ht="15.75" customHeight="1">
       <c r="A339" s="1" t="s">
         <v>1156</v>
       </c>
@@ -21249,7 +21251,7 @@
       <c r="U339" s="3"/>
       <c r="AA339" s="1"/>
     </row>
-    <row r="340" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:27" ht="15.75" customHeight="1">
       <c r="A340" s="1" t="s">
         <v>1157</v>
       </c>
@@ -21281,7 +21283,7 @@
       <c r="U340" s="3"/>
       <c r="AA340" s="1"/>
     </row>
-    <row r="341" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:27" ht="15.75" customHeight="1">
       <c r="A341" s="1" t="s">
         <v>1158</v>
       </c>
@@ -21313,7 +21315,7 @@
       <c r="U341" s="3"/>
       <c r="AA341" s="1"/>
     </row>
-    <row r="342" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:27" ht="15.75" customHeight="1">
       <c r="A342" s="1" t="s">
         <v>1159</v>
       </c>
@@ -21345,7 +21347,7 @@
       <c r="U342" s="3"/>
       <c r="AA342" s="1"/>
     </row>
-    <row r="343" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:27" ht="15.75" customHeight="1">
       <c r="A343" s="1" t="s">
         <v>1160</v>
       </c>
@@ -21377,7 +21379,7 @@
       <c r="U343" s="3"/>
       <c r="AA343" s="1"/>
     </row>
-    <row r="344" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:27" ht="15.75" customHeight="1">
       <c r="A344" s="1" t="s">
         <v>1161</v>
       </c>
@@ -21409,7 +21411,7 @@
       <c r="U344" s="3"/>
       <c r="AA344" s="1"/>
     </row>
-    <row r="345" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:27" ht="15.75" customHeight="1">
       <c r="A345" s="1" t="s">
         <v>1162</v>
       </c>
@@ -21441,7 +21443,7 @@
       <c r="U345" s="3"/>
       <c r="AA345" s="1"/>
     </row>
-    <row r="346" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:27" ht="15.75" customHeight="1">
       <c r="A346" s="1" t="s">
         <v>1163</v>
       </c>
@@ -21473,7 +21475,7 @@
       <c r="U346" s="3"/>
       <c r="AA346" s="1"/>
     </row>
-    <row r="347" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:27" ht="15.75" customHeight="1">
       <c r="A347" s="1" t="s">
         <v>1164</v>
       </c>
@@ -21505,7 +21507,7 @@
       <c r="U347" s="3"/>
       <c r="AA347" s="1"/>
     </row>
-    <row r="348" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:27" ht="15.75" customHeight="1">
       <c r="A348" s="1" t="s">
         <v>1165</v>
       </c>
@@ -21537,7 +21539,7 @@
       <c r="U348" s="3"/>
       <c r="AA348" s="1"/>
     </row>
-    <row r="349" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:27" ht="15.75" customHeight="1">
       <c r="A349" s="1" t="s">
         <v>1166</v>
       </c>
@@ -21569,7 +21571,7 @@
       <c r="U349" s="3"/>
       <c r="AA349" s="1"/>
     </row>
-    <row r="350" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:27" ht="15.75" customHeight="1">
       <c r="A350" s="1" t="s">
         <v>1167</v>
       </c>
@@ -21601,7 +21603,7 @@
       <c r="U350" s="3"/>
       <c r="AA350" s="1"/>
     </row>
-    <row r="351" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:27" ht="15.75" customHeight="1">
       <c r="A351" s="1" t="s">
         <v>1168</v>
       </c>
@@ -21633,7 +21635,7 @@
       <c r="U351" s="3"/>
       <c r="AA351" s="1"/>
     </row>
-    <row r="352" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:27" ht="15.75" customHeight="1">
       <c r="A352" s="1" t="s">
         <v>1169</v>
       </c>
@@ -21665,7 +21667,7 @@
       <c r="U352" s="3"/>
       <c r="AA352" s="1"/>
     </row>
-    <row r="353" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:27" ht="15.75" customHeight="1">
       <c r="A353" s="1" t="s">
         <v>1170</v>
       </c>
@@ -21697,7 +21699,7 @@
       <c r="U353" s="3"/>
       <c r="AA353" s="1"/>
     </row>
-    <row r="354" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:27" ht="15.75" customHeight="1">
       <c r="A354" s="1" t="s">
         <v>1171</v>
       </c>
@@ -21729,7 +21731,7 @@
       <c r="U354" s="3"/>
       <c r="AA354" s="1"/>
     </row>
-    <row r="355" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:27" ht="15.75" customHeight="1">
       <c r="A355" s="1" t="s">
         <v>1173</v>
       </c>
@@ -21761,7 +21763,7 @@
       <c r="U355" s="3"/>
       <c r="AA355" s="1"/>
     </row>
-    <row r="356" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:27" ht="15.75" customHeight="1">
       <c r="A356" s="1" t="s">
         <v>1174</v>
       </c>
@@ -21793,7 +21795,7 @@
       <c r="U356" s="3"/>
       <c r="AA356" s="1"/>
     </row>
-    <row r="357" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:27" ht="15.75" customHeight="1">
       <c r="A357" s="1" t="s">
         <v>1175</v>
       </c>
@@ -21825,7 +21827,7 @@
       <c r="U357" s="3"/>
       <c r="AA357" s="1"/>
     </row>
-    <row r="358" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:27" ht="15.75" customHeight="1">
       <c r="A358" s="1" t="s">
         <v>1176</v>
       </c>
@@ -21857,7 +21859,7 @@
       <c r="U358" s="3"/>
       <c r="AA358" s="1"/>
     </row>
-    <row r="359" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:27" ht="15.75" customHeight="1">
       <c r="A359" s="1" t="s">
         <v>1178</v>
       </c>
@@ -21889,7 +21891,7 @@
       <c r="U359" s="3"/>
       <c r="AA359" s="1"/>
     </row>
-    <row r="360" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:27" ht="15.75" customHeight="1">
       <c r="A360" s="1" t="s">
         <v>1179</v>
       </c>
@@ -21921,7 +21923,7 @@
       <c r="U360" s="3"/>
       <c r="AA360" s="1"/>
     </row>
-    <row r="361" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:27" ht="15.75" customHeight="1">
       <c r="A361" s="1" t="s">
         <v>1180</v>
       </c>
@@ -21953,7 +21955,7 @@
       <c r="U361" s="3"/>
       <c r="AA361" s="1"/>
     </row>
-    <row r="362" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:27" ht="15.75" customHeight="1">
       <c r="A362" s="1" t="s">
         <v>1181</v>
       </c>
@@ -21985,7 +21987,7 @@
       <c r="U362" s="3"/>
       <c r="AA362" s="1"/>
     </row>
-    <row r="363" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:27" ht="15.75" customHeight="1">
       <c r="A363" s="1" t="s">
         <v>1182</v>
       </c>
@@ -22017,7 +22019,7 @@
       <c r="U363" s="3"/>
       <c r="AA363" s="1"/>
     </row>
-    <row r="364" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:27" ht="15.75" customHeight="1">
       <c r="A364" s="1" t="s">
         <v>1183</v>
       </c>
@@ -22049,7 +22051,7 @@
       <c r="U364" s="3"/>
       <c r="AA364" s="1"/>
     </row>
-    <row r="365" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:27" ht="15.75" customHeight="1">
       <c r="A365" s="1" t="s">
         <v>1184</v>
       </c>
@@ -22081,7 +22083,7 @@
       <c r="U365" s="3"/>
       <c r="AA365" s="1"/>
     </row>
-    <row r="366" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:27" ht="15.75" customHeight="1">
       <c r="A366" s="1" t="s">
         <v>1185</v>
       </c>
@@ -22113,7 +22115,7 @@
       <c r="U366" s="3"/>
       <c r="AA366" s="1"/>
     </row>
-    <row r="367" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:27" ht="15.75" customHeight="1">
       <c r="A367" s="1" t="s">
         <v>1186</v>
       </c>
@@ -22145,7 +22147,7 @@
       <c r="U367" s="3"/>
       <c r="AA367" s="1"/>
     </row>
-    <row r="368" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:27" ht="15.75" customHeight="1">
       <c r="A368" s="1" t="s">
         <v>1187</v>
       </c>
@@ -22177,7 +22179,7 @@
       <c r="U368" s="3"/>
       <c r="AA368" s="1"/>
     </row>
-    <row r="369" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:27" ht="15.75" customHeight="1">
       <c r="A369" s="1" t="s">
         <v>1188</v>
       </c>
@@ -22209,7 +22211,7 @@
       <c r="U369" s="3"/>
       <c r="AA369" s="1"/>
     </row>
-    <row r="370" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:27" ht="15.75" customHeight="1">
       <c r="A370" s="1" t="s">
         <v>1189</v>
       </c>
@@ -22241,7 +22243,7 @@
       <c r="U370" s="3"/>
       <c r="AA370" s="1"/>
     </row>
-    <row r="371" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:27" ht="15.75" customHeight="1">
       <c r="A371" s="1" t="s">
         <v>1190</v>
       </c>
@@ -22273,7 +22275,7 @@
       <c r="U371" s="3"/>
       <c r="AA371" s="1"/>
     </row>
-    <row r="372" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:27" ht="15.75" customHeight="1">
       <c r="A372" s="1" t="s">
         <v>1191</v>
       </c>
@@ -22305,7 +22307,7 @@
       <c r="U372" s="3"/>
       <c r="AA372" s="1"/>
     </row>
-    <row r="373" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:27" ht="15.75" customHeight="1">
       <c r="A373" s="1" t="s">
         <v>1192</v>
       </c>
@@ -22337,7 +22339,7 @@
       <c r="U373" s="3"/>
       <c r="AA373" s="1"/>
     </row>
-    <row r="374" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:27" ht="15.75" customHeight="1">
       <c r="A374" s="1" t="s">
         <v>1193</v>
       </c>
@@ -22369,7 +22371,7 @@
       <c r="U374" s="3"/>
       <c r="AA374" s="1"/>
     </row>
-    <row r="375" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:27" ht="15.75" customHeight="1">
       <c r="A375" s="1" t="s">
         <v>1194</v>
       </c>
@@ -22401,7 +22403,7 @@
       <c r="U375" s="3"/>
       <c r="AA375" s="1"/>
     </row>
-    <row r="376" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:27" ht="15.75" customHeight="1">
       <c r="A376" s="1" t="s">
         <v>1195</v>
       </c>
@@ -22433,7 +22435,7 @@
       <c r="U376" s="3"/>
       <c r="AA376" s="1"/>
     </row>
-    <row r="377" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:27" ht="15.75" customHeight="1">
       <c r="A377" s="1" t="s">
         <v>1196</v>
       </c>
@@ -22465,7 +22467,7 @@
       <c r="U377" s="3"/>
       <c r="AA377" s="1"/>
     </row>
-    <row r="378" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:27" ht="15.75" customHeight="1">
       <c r="A378" s="1" t="s">
         <v>1197</v>
       </c>
@@ -22497,7 +22499,7 @@
       <c r="U378" s="3"/>
       <c r="AA378" s="1"/>
     </row>
-    <row r="379" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:27" ht="15.75" customHeight="1">
       <c r="A379" s="1" t="s">
         <v>1198</v>
       </c>
@@ -22529,7 +22531,7 @@
       <c r="U379" s="3"/>
       <c r="AA379" s="1"/>
     </row>
-    <row r="380" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:27" ht="15.75" customHeight="1">
       <c r="A380" s="1" t="s">
         <v>1199</v>
       </c>
@@ -22561,7 +22563,7 @@
       <c r="U380" s="3"/>
       <c r="AA380" s="1"/>
     </row>
-    <row r="381" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:27" ht="15.75" customHeight="1">
       <c r="A381" s="1" t="s">
         <v>1200</v>
       </c>
@@ -22593,7 +22595,7 @@
       <c r="U381" s="3"/>
       <c r="AA381" s="1"/>
     </row>
-    <row r="382" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:27" ht="15.75" customHeight="1">
       <c r="A382" s="1" t="s">
         <v>1201</v>
       </c>
@@ -22625,7 +22627,7 @@
       <c r="U382" s="3"/>
       <c r="AA382" s="1"/>
     </row>
-    <row r="383" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:27" ht="15.75" customHeight="1">
       <c r="A383" s="1" t="s">
         <v>1202</v>
       </c>
@@ -22657,7 +22659,7 @@
       <c r="U383" s="3"/>
       <c r="AA383" s="1"/>
     </row>
-    <row r="384" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:27" ht="15.75" customHeight="1">
       <c r="A384" s="1" t="s">
         <v>1203</v>
       </c>
@@ -22689,7 +22691,7 @@
       <c r="U384" s="3"/>
       <c r="AA384" s="1"/>
     </row>
-    <row r="385" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:27" ht="15.75" customHeight="1">
       <c r="A385" s="1" t="s">
         <v>1204</v>
       </c>
@@ -22721,7 +22723,7 @@
       <c r="U385" s="3"/>
       <c r="AA385" s="1"/>
     </row>
-    <row r="386" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:27" ht="15.75" customHeight="1">
       <c r="A386" s="1" t="s">
         <v>1205</v>
       </c>
@@ -22753,7 +22755,7 @@
       <c r="U386" s="3"/>
       <c r="AA386" s="1"/>
     </row>
-    <row r="387" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:27" ht="15.75" customHeight="1">
       <c r="A387" s="1" t="s">
         <v>1206</v>
       </c>
@@ -22785,7 +22787,7 @@
       <c r="U387" s="3"/>
       <c r="AA387" s="1"/>
     </row>
-    <row r="388" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:27" ht="15.75" customHeight="1">
       <c r="A388" s="1" t="s">
         <v>1207</v>
       </c>
@@ -22817,7 +22819,7 @@
       <c r="U388" s="3"/>
       <c r="AA388" s="1"/>
     </row>
-    <row r="389" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:27" ht="15.75" customHeight="1">
       <c r="A389" s="1" t="s">
         <v>1208</v>
       </c>
@@ -22849,7 +22851,7 @@
       <c r="U389" s="3"/>
       <c r="AA389" s="1"/>
     </row>
-    <row r="390" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:27" ht="15.75" customHeight="1">
       <c r="A390" s="1" t="s">
         <v>1209</v>
       </c>
@@ -22881,7 +22883,7 @@
       <c r="U390" s="3"/>
       <c r="AA390" s="1"/>
     </row>
-    <row r="391" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:27" ht="15.75" customHeight="1">
       <c r="A391" s="1" t="s">
         <v>1210</v>
       </c>
@@ -22913,7 +22915,7 @@
       <c r="U391" s="3"/>
       <c r="AA391" s="1"/>
     </row>
-    <row r="392" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:27" ht="15.75" customHeight="1">
       <c r="A392" s="1" t="s">
         <v>1211</v>
       </c>
@@ -22945,7 +22947,7 @@
       <c r="U392" s="3"/>
       <c r="AA392" s="1"/>
     </row>
-    <row r="393" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:27" ht="15.75" customHeight="1">
       <c r="A393" s="1" t="s">
         <v>1212</v>
       </c>
@@ -22977,7 +22979,7 @@
       <c r="U393" s="3"/>
       <c r="AA393" s="1"/>
     </row>
-    <row r="394" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:27" ht="15.75" customHeight="1">
       <c r="A394" s="1" t="s">
         <v>1213</v>
       </c>
@@ -23009,7 +23011,7 @@
       <c r="U394" s="3"/>
       <c r="AA394" s="1"/>
     </row>
-    <row r="395" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:27" ht="15.75" customHeight="1">
       <c r="A395" s="1" t="s">
         <v>1214</v>
       </c>
@@ -23041,7 +23043,7 @@
       <c r="U395" s="3"/>
       <c r="AA395" s="1"/>
     </row>
-    <row r="396" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:27" ht="15.75" customHeight="1">
       <c r="A396" s="1" t="s">
         <v>1215</v>
       </c>
@@ -23073,7 +23075,7 @@
       <c r="U396" s="3"/>
       <c r="AA396" s="1"/>
     </row>
-    <row r="397" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:27" ht="15.75" customHeight="1">
       <c r="A397" s="1" t="s">
         <v>1216</v>
       </c>
@@ -23105,7 +23107,7 @@
       <c r="U397" s="3"/>
       <c r="AA397" s="1"/>
     </row>
-    <row r="398" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:27" ht="15.75" customHeight="1">
       <c r="A398" s="1" t="s">
         <v>1217</v>
       </c>
@@ -23137,7 +23139,7 @@
       <c r="U398" s="3"/>
       <c r="AA398" s="1"/>
     </row>
-    <row r="399" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:27" ht="15.75" customHeight="1">
       <c r="A399" s="1" t="s">
         <v>1218</v>
       </c>
@@ -23169,7 +23171,7 @@
       <c r="U399" s="3"/>
       <c r="AA399" s="1"/>
     </row>
-    <row r="400" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:27" ht="15.75" customHeight="1">
       <c r="A400" s="1" t="s">
         <v>1219</v>
       </c>
@@ -23201,7 +23203,7 @@
       <c r="U400" s="3"/>
       <c r="AA400" s="1"/>
     </row>
-    <row r="401" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:27" ht="15.75" customHeight="1">
       <c r="A401" s="1" t="s">
         <v>1220</v>
       </c>
@@ -23233,7 +23235,7 @@
       <c r="U401" s="3"/>
       <c r="AA401" s="1"/>
     </row>
-    <row r="402" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:27" ht="15.75" customHeight="1">
       <c r="A402" s="1" t="s">
         <v>1221</v>
       </c>
@@ -23265,7 +23267,7 @@
       <c r="U402" s="3"/>
       <c r="AA402" s="1"/>
     </row>
-    <row r="403" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:27" ht="15.75" customHeight="1">
       <c r="A403" s="1" t="s">
         <v>1222</v>
       </c>
@@ -23297,7 +23299,7 @@
       <c r="U403" s="3"/>
       <c r="AA403" s="1"/>
     </row>
-    <row r="404" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:27" ht="15.75" customHeight="1">
       <c r="A404" s="1" t="s">
         <v>1223</v>
       </c>
@@ -23329,7 +23331,7 @@
       <c r="U404" s="3"/>
       <c r="AA404" s="1"/>
     </row>
-    <row r="405" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:27" ht="15.75" customHeight="1">
       <c r="A405" s="1" t="s">
         <v>1225</v>
       </c>
@@ -23361,7 +23363,7 @@
       <c r="U405" s="3"/>
       <c r="AA405" s="1"/>
     </row>
-    <row r="406" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:27" ht="15.75" customHeight="1">
       <c r="A406" s="1" t="s">
         <v>1226</v>
       </c>
@@ -23393,7 +23395,7 @@
       <c r="U406" s="3"/>
       <c r="AA406" s="1"/>
     </row>
-    <row r="407" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:27" ht="15.75" customHeight="1">
       <c r="A407" s="1" t="s">
         <v>1227</v>
       </c>
@@ -23425,7 +23427,7 @@
       <c r="U407" s="3"/>
       <c r="AA407" s="1"/>
     </row>
-    <row r="408" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:27" ht="15.75" customHeight="1">
       <c r="A408" s="1" t="s">
         <v>1229</v>
       </c>
@@ -23457,7 +23459,7 @@
       <c r="U408" s="3"/>
       <c r="AA408" s="1"/>
     </row>
-    <row r="409" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:27" ht="15.75" customHeight="1">
       <c r="A409" s="1" t="s">
         <v>1230</v>
       </c>
@@ -23489,7 +23491,7 @@
       <c r="U409" s="3"/>
       <c r="AA409" s="1"/>
     </row>
-    <row r="410" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:27" ht="15.75" customHeight="1">
       <c r="A410" s="1" t="s">
         <v>1231</v>
       </c>
@@ -23521,7 +23523,7 @@
       <c r="U410" s="3"/>
       <c r="AA410" s="1"/>
     </row>
-    <row r="411" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:27" ht="15.75" customHeight="1">
       <c r="A411" s="1" t="s">
         <v>1232</v>
       </c>
@@ -23552,7 +23554,7 @@
       <c r="U411" s="3"/>
       <c r="AA411" s="1"/>
     </row>
-    <row r="412" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:27" ht="15.75" customHeight="1">
       <c r="A412" s="1" t="s">
         <v>1233</v>
       </c>
@@ -23584,7 +23586,7 @@
       <c r="U412" s="3"/>
       <c r="AA412" s="1"/>
     </row>
-    <row r="413" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:27" ht="15.75" customHeight="1">
       <c r="A413" s="1" t="s">
         <v>1234</v>
       </c>
@@ -23616,7 +23618,7 @@
       <c r="U413" s="3"/>
       <c r="AA413" s="1"/>
     </row>
-    <row r="414" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:27" ht="15.75" customHeight="1">
       <c r="A414" s="1" t="s">
         <v>1235</v>
       </c>
@@ -23648,7 +23650,7 @@
       <c r="U414" s="3"/>
       <c r="AA414" s="1"/>
     </row>
-    <row r="415" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:27" ht="15.75" customHeight="1">
       <c r="A415" s="1" t="s">
         <v>1236</v>
       </c>
@@ -23674,7 +23676,7 @@
       <c r="U415" s="3"/>
       <c r="AA415" s="1"/>
     </row>
-    <row r="416" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:27" ht="15.75" customHeight="1">
       <c r="A416" s="1" t="s">
         <v>1237</v>
       </c>
@@ -23700,7 +23702,7 @@
       <c r="U416" s="3"/>
       <c r="AA416" s="1"/>
     </row>
-    <row r="417" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:27" ht="15.75" customHeight="1">
       <c r="A417" s="1" t="s">
         <v>1238</v>
       </c>
@@ -23726,7 +23728,7 @@
       <c r="U417" s="3"/>
       <c r="AA417" s="1"/>
     </row>
-    <row r="418" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:27" ht="15.75" customHeight="1">
       <c r="A418" s="1" t="s">
         <v>1239</v>
       </c>
@@ -23752,7 +23754,7 @@
       <c r="U418" s="3"/>
       <c r="AA418" s="1"/>
     </row>
-    <row r="419" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:27" ht="15.75" customHeight="1">
       <c r="A419" s="1" t="s">
         <v>1240</v>
       </c>
@@ -23778,7 +23780,7 @@
       <c r="U419" s="3"/>
       <c r="AA419" s="1"/>
     </row>
-    <row r="420" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:27" ht="15.75" customHeight="1">
       <c r="A420" s="1" t="s">
         <v>1241</v>
       </c>
@@ -23804,7 +23806,7 @@
       <c r="U420" s="3"/>
       <c r="AA420" s="1"/>
     </row>
-    <row r="421" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:27" ht="15.75" customHeight="1">
       <c r="A421" s="1" t="s">
         <v>1242</v>
       </c>
@@ -23830,7 +23832,7 @@
       <c r="U421" s="3"/>
       <c r="AA421" s="1"/>
     </row>
-    <row r="422" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:27" ht="15.75" customHeight="1">
       <c r="A422" s="1" t="s">
         <v>1243</v>
       </c>
@@ -23856,7 +23858,7 @@
       <c r="U422" s="3"/>
       <c r="AA422" s="1"/>
     </row>
-    <row r="423" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:27" ht="15.75" customHeight="1">
       <c r="A423" s="1" t="s">
         <v>1244</v>
       </c>
@@ -23882,7 +23884,7 @@
       <c r="U423" s="3"/>
       <c r="AA423" s="1"/>
     </row>
-    <row r="424" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:27" ht="15.75" customHeight="1">
       <c r="A424" s="1" t="s">
         <v>1245</v>
       </c>
@@ -23908,7 +23910,7 @@
       <c r="U424" s="3"/>
       <c r="AA424" s="1"/>
     </row>
-    <row r="425" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:27" ht="15.75" customHeight="1">
       <c r="A425" s="1" t="s">
         <v>1246</v>
       </c>
@@ -23934,7 +23936,7 @@
       <c r="U425" s="3"/>
       <c r="AA425" s="1"/>
     </row>
-    <row r="426" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:27" ht="15.75" customHeight="1">
       <c r="A426" s="1" t="s">
         <v>1247</v>
       </c>
@@ -23960,7 +23962,7 @@
       <c r="U426" s="3"/>
       <c r="AA426" s="1"/>
     </row>
-    <row r="427" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:27" ht="15.75" customHeight="1">
       <c r="A427" s="1" t="s">
         <v>1248</v>
       </c>
@@ -23986,7 +23988,7 @@
       <c r="U427" s="3"/>
       <c r="AA427" s="1"/>
     </row>
-    <row r="428" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:27" ht="15.75" customHeight="1">
       <c r="A428" s="1" t="s">
         <v>1249</v>
       </c>
@@ -24012,7 +24014,7 @@
       <c r="U428" s="3"/>
       <c r="AA428" s="1"/>
     </row>
-    <row r="429" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:27" ht="15.75" customHeight="1">
       <c r="A429" s="1" t="s">
         <v>1250</v>
       </c>
@@ -24038,7 +24040,7 @@
       <c r="U429" s="3"/>
       <c r="AA429" s="1"/>
     </row>
-    <row r="430" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:27" ht="15.75" customHeight="1">
       <c r="A430" s="1" t="s">
         <v>1251</v>
       </c>
@@ -24064,7 +24066,7 @@
       <c r="U430" s="3"/>
       <c r="AA430" s="1"/>
     </row>
-    <row r="431" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:27" ht="15.75" customHeight="1">
       <c r="A431" s="1" t="s">
         <v>1252</v>
       </c>
@@ -24090,7 +24092,7 @@
       <c r="U431" s="3"/>
       <c r="AA431" s="1"/>
     </row>
-    <row r="432" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:27" ht="15.75" customHeight="1">
       <c r="A432" s="1" t="s">
         <v>1253</v>
       </c>
@@ -24116,7 +24118,7 @@
       <c r="U432" s="3"/>
       <c r="AA432" s="1"/>
     </row>
-    <row r="433" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:27" ht="15.75" customHeight="1">
       <c r="A433" s="1" t="s">
         <v>1254</v>
       </c>
@@ -24142,7 +24144,7 @@
       <c r="U433" s="3"/>
       <c r="AA433" s="1"/>
     </row>
-    <row r="434" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:27" ht="15.75" customHeight="1">
       <c r="A434" s="1" t="s">
         <v>1255</v>
       </c>
@@ -24168,7 +24170,7 @@
       <c r="U434" s="3"/>
       <c r="AA434" s="1"/>
     </row>
-    <row r="435" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:27" ht="15.75" customHeight="1">
       <c r="A435" s="1" t="s">
         <v>1256</v>
       </c>
@@ -24194,7 +24196,7 @@
       <c r="U435" s="3"/>
       <c r="AA435" s="1"/>
     </row>
-    <row r="436" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:27" ht="15.75" customHeight="1">
       <c r="A436" s="1" t="s">
         <v>1257</v>
       </c>
@@ -24220,7 +24222,7 @@
       <c r="U436" s="3"/>
       <c r="AA436" s="1"/>
     </row>
-    <row r="437" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:27" ht="15.75" customHeight="1">
       <c r="A437" s="1" t="s">
         <v>1258</v>
       </c>
@@ -24246,7 +24248,7 @@
       <c r="U437" s="3"/>
       <c r="AA437" s="1"/>
     </row>
-    <row r="438" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:27" ht="15.75" customHeight="1">
       <c r="A438" s="1" t="s">
         <v>1259</v>
       </c>
@@ -24272,7 +24274,7 @@
       <c r="U438" s="3"/>
       <c r="AA438" s="1"/>
     </row>
-    <row r="439" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:27" ht="15.75" customHeight="1">
       <c r="A439" s="1" t="s">
         <v>1260</v>
       </c>
@@ -24298,7 +24300,7 @@
       <c r="U439" s="3"/>
       <c r="AA439" s="1"/>
     </row>
-    <row r="440" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:27" ht="15.75" customHeight="1">
       <c r="A440" s="1" t="s">
         <v>1261</v>
       </c>
@@ -24324,7 +24326,7 @@
       <c r="U440" s="3"/>
       <c r="AA440" s="1"/>
     </row>
-    <row r="441" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:27" ht="15.75" customHeight="1">
       <c r="A441" s="1" t="s">
         <v>1262</v>
       </c>
@@ -24350,7 +24352,7 @@
       <c r="U441" s="3"/>
       <c r="AA441" s="1"/>
     </row>
-    <row r="442" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:27" ht="15.75" customHeight="1">
       <c r="A442" s="1" t="s">
         <v>1263</v>
       </c>
@@ -24376,7 +24378,7 @@
       <c r="U442" s="3"/>
       <c r="AA442" s="1"/>
     </row>
-    <row r="443" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:27" ht="15.75" customHeight="1">
       <c r="A443" s="1" t="s">
         <v>1264</v>
       </c>
@@ -24402,7 +24404,7 @@
       <c r="U443" s="3"/>
       <c r="AA443" s="1"/>
     </row>
-    <row r="444" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:27" ht="15.75" customHeight="1">
       <c r="A444" s="1" t="s">
         <v>1265</v>
       </c>
@@ -24428,7 +24430,7 @@
       <c r="U444" s="3"/>
       <c r="AA444" s="1"/>
     </row>
-    <row r="445" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:27" ht="15.75" customHeight="1">
       <c r="A445" s="1" t="s">
         <v>1266</v>
       </c>
@@ -24454,7 +24456,7 @@
       <c r="U445" s="3"/>
       <c r="AA445" s="1"/>
     </row>
-    <row r="446" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:27" ht="15.75" customHeight="1">
       <c r="A446" s="1" t="s">
         <v>1267</v>
       </c>
@@ -24480,7 +24482,7 @@
       <c r="U446" s="3"/>
       <c r="AA446" s="1"/>
     </row>
-    <row r="447" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:27" ht="15.75" customHeight="1">
       <c r="A447" s="1" t="s">
         <v>1268</v>
       </c>
@@ -24506,7 +24508,7 @@
       <c r="U447" s="3"/>
       <c r="AA447" s="1"/>
     </row>
-    <row r="448" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:27" ht="15.75" customHeight="1">
       <c r="A448" s="1" t="s">
         <v>1269</v>
       </c>
@@ -24532,7 +24534,7 @@
       <c r="U448" s="3"/>
       <c r="AA448" s="1"/>
     </row>
-    <row r="449" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:27" ht="15.75" customHeight="1">
       <c r="A449" s="1" t="s">
         <v>1270</v>
       </c>
@@ -24558,7 +24560,7 @@
       <c r="U449" s="3"/>
       <c r="AA449" s="1"/>
     </row>
-    <row r="450" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:27" ht="15.75" customHeight="1">
       <c r="A450" s="1" t="s">
         <v>1271</v>
       </c>
@@ -24584,7 +24586,7 @@
       <c r="U450" s="3"/>
       <c r="AA450" s="1"/>
     </row>
-    <row r="451" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:27" ht="15.75" customHeight="1">
       <c r="A451" s="1" t="s">
         <v>1272</v>
       </c>
@@ -24610,7 +24612,7 @@
       <c r="U451" s="3"/>
       <c r="AA451" s="1"/>
     </row>
-    <row r="452" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:27" ht="15.75" customHeight="1">
       <c r="A452" s="1" t="s">
         <v>1273</v>
       </c>
@@ -24636,7 +24638,7 @@
       <c r="U452" s="3"/>
       <c r="AA452" s="1"/>
     </row>
-    <row r="453" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:27" ht="15.75" customHeight="1">
       <c r="A453" s="1" t="s">
         <v>1274</v>
       </c>
@@ -24662,7 +24664,7 @@
       <c r="U453" s="3"/>
       <c r="AA453" s="1"/>
     </row>
-    <row r="454" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:27" ht="15.75" customHeight="1">
       <c r="A454" s="1" t="s">
         <v>1275</v>
       </c>
@@ -24688,7 +24690,7 @@
       <c r="U454" s="3"/>
       <c r="AA454" s="1"/>
     </row>
-    <row r="455" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:27" ht="15.75" customHeight="1">
       <c r="A455" s="1" t="s">
         <v>1276</v>
       </c>
@@ -24714,7 +24716,7 @@
       <c r="U455" s="3"/>
       <c r="AA455" s="1"/>
     </row>
-    <row r="456" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:27" ht="15.75" customHeight="1">
       <c r="A456" s="1" t="s">
         <v>1277</v>
       </c>
@@ -24740,7 +24742,7 @@
       <c r="U456" s="3"/>
       <c r="AA456" s="1"/>
     </row>
-    <row r="457" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:27" ht="15.75" customHeight="1">
       <c r="A457" s="1" t="s">
         <v>1278</v>
       </c>
@@ -24766,7 +24768,7 @@
       <c r="U457" s="3"/>
       <c r="AA457" s="1"/>
     </row>
-    <row r="458" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:27" ht="15.75" customHeight="1">
       <c r="A458" s="1" t="s">
         <v>1279</v>
       </c>
@@ -24792,7 +24794,7 @@
       <c r="U458" s="3"/>
       <c r="AA458" s="1"/>
     </row>
-    <row r="459" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:27" ht="15.75" customHeight="1">
       <c r="A459" s="1" t="s">
         <v>1280</v>
       </c>
@@ -24818,7 +24820,7 @@
       <c r="U459" s="3"/>
       <c r="AA459" s="1"/>
     </row>
-    <row r="460" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:27" ht="15.75" customHeight="1">
       <c r="A460" s="1" t="s">
         <v>1281</v>
       </c>
@@ -24844,7 +24846,7 @@
       <c r="U460" s="3"/>
       <c r="AA460" s="1"/>
     </row>
-    <row r="461" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:27" ht="15.75" customHeight="1">
       <c r="A461" s="1" t="s">
         <v>1282</v>
       </c>
@@ -24870,7 +24872,7 @@
       <c r="U461" s="3"/>
       <c r="AA461" s="1"/>
     </row>
-    <row r="462" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:27" ht="15.75" customHeight="1">
       <c r="A462" s="1" t="s">
         <v>1283</v>
       </c>
@@ -24896,7 +24898,7 @@
       <c r="U462" s="3"/>
       <c r="AA462" s="1"/>
     </row>
-    <row r="463" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:27" ht="15.75" customHeight="1">
       <c r="A463" s="1" t="s">
         <v>1284</v>
       </c>
@@ -24922,7 +24924,7 @@
       <c r="U463" s="3"/>
       <c r="AA463" s="1"/>
     </row>
-    <row r="464" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:27" ht="15.75" customHeight="1">
       <c r="A464" s="1" t="s">
         <v>1285</v>
       </c>
@@ -24948,7 +24950,7 @@
       <c r="U464" s="3"/>
       <c r="AA464" s="1"/>
     </row>
-    <row r="465" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:27" ht="15.75" customHeight="1">
       <c r="A465" s="1" t="s">
         <v>1286</v>
       </c>
@@ -24974,7 +24976,7 @@
       <c r="U465" s="3"/>
       <c r="AA465" s="1"/>
     </row>
-    <row r="466" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:27" ht="15.75" customHeight="1">
       <c r="A466" s="1" t="s">
         <v>1287</v>
       </c>
@@ -25000,7 +25002,7 @@
       <c r="U466" s="3"/>
       <c r="AA466" s="1"/>
     </row>
-    <row r="467" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:27" ht="15.75" customHeight="1">
       <c r="A467" s="1" t="s">
         <v>1288</v>
       </c>
@@ -25026,7 +25028,7 @@
       <c r="U467" s="3"/>
       <c r="AA467" s="1"/>
     </row>
-    <row r="468" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:27" ht="15.75" customHeight="1">
       <c r="A468" s="1" t="s">
         <v>1289</v>
       </c>
@@ -25052,7 +25054,7 @@
       <c r="U468" s="3"/>
       <c r="AA468" s="1"/>
     </row>
-    <row r="469" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:27" ht="15.75" customHeight="1">
       <c r="A469" s="1" t="s">
         <v>1290</v>
       </c>
@@ -25078,7 +25080,7 @@
       <c r="U469" s="3"/>
       <c r="AA469" s="1"/>
     </row>
-    <row r="470" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:27" ht="15.75" customHeight="1">
       <c r="A470" s="1" t="s">
         <v>1291</v>
       </c>
@@ -25104,7 +25106,7 @@
       <c r="U470" s="3"/>
       <c r="AA470" s="1"/>
     </row>
-    <row r="471" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:27" ht="15.75" customHeight="1">
       <c r="A471" s="1" t="s">
         <v>1292</v>
       </c>
@@ -25130,7 +25132,7 @@
       <c r="U471" s="3"/>
       <c r="AA471" s="1"/>
     </row>
-    <row r="472" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:27" ht="15.75" customHeight="1">
       <c r="A472" s="1" t="s">
         <v>1293</v>
       </c>
@@ -25156,7 +25158,7 @@
       <c r="U472" s="3"/>
       <c r="AA472" s="1"/>
     </row>
-    <row r="473" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:27" ht="15.75" customHeight="1">
       <c r="A473" s="1" t="s">
         <v>1294</v>
       </c>
@@ -25182,7 +25184,7 @@
       <c r="U473" s="3"/>
       <c r="AA473" s="1"/>
     </row>
-    <row r="474" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:27" ht="15.75" customHeight="1">
       <c r="A474" s="1" t="s">
         <v>1295</v>
       </c>
@@ -25208,7 +25210,7 @@
       <c r="U474" s="3"/>
       <c r="AA474" s="1"/>
     </row>
-    <row r="475" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:27" ht="15.75" customHeight="1">
       <c r="A475" s="1" t="s">
         <v>1296</v>
       </c>
@@ -25234,7 +25236,7 @@
       <c r="U475" s="3"/>
       <c r="AA475" s="1"/>
     </row>
-    <row r="476" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:27" ht="15.75" customHeight="1">
       <c r="A476" s="1" t="s">
         <v>1297</v>
       </c>
@@ -25260,7 +25262,7 @@
       <c r="U476" s="3"/>
       <c r="AA476" s="1"/>
     </row>
-    <row r="477" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:27" ht="15.75" customHeight="1">
       <c r="A477" s="1" t="s">
         <v>1298</v>
       </c>
@@ -25286,7 +25288,7 @@
       <c r="U477" s="3"/>
       <c r="AA477" s="1"/>
     </row>
-    <row r="478" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:27" ht="15.75" customHeight="1">
       <c r="A478" s="1" t="s">
         <v>1299</v>
       </c>
@@ -25312,7 +25314,7 @@
       <c r="U478" s="3"/>
       <c r="AA478" s="1"/>
     </row>
-    <row r="479" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:27" ht="15.75" customHeight="1">
       <c r="A479" s="1" t="s">
         <v>1300</v>
       </c>
@@ -25338,7 +25340,7 @@
       <c r="U479" s="3"/>
       <c r="AA479" s="1"/>
     </row>
-    <row r="480" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:27" ht="15.75" customHeight="1">
       <c r="A480" s="1" t="s">
         <v>1301</v>
       </c>
@@ -25364,7 +25366,7 @@
       <c r="U480" s="3"/>
       <c r="AA480" s="1"/>
     </row>
-    <row r="481" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:27" ht="15.75" customHeight="1">
       <c r="A481" s="1" t="s">
         <v>1302</v>
       </c>
@@ -25390,7 +25392,7 @@
       <c r="U481" s="3"/>
       <c r="AA481" s="1"/>
     </row>
-    <row r="482" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:27" ht="15.75" customHeight="1">
       <c r="A482" s="1" t="s">
         <v>1303</v>
       </c>
@@ -25416,7 +25418,7 @@
       <c r="U482" s="3"/>
       <c r="AA482" s="1"/>
     </row>
-    <row r="483" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:27" ht="15.75" customHeight="1">
       <c r="A483" s="1" t="s">
         <v>1304</v>
       </c>
@@ -25442,7 +25444,7 @@
       <c r="U483" s="3"/>
       <c r="AA483" s="1"/>
     </row>
-    <row r="484" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:27" ht="15.75" customHeight="1">
       <c r="A484" s="1" t="s">
         <v>1305</v>
       </c>
@@ -25468,7 +25470,7 @@
       <c r="U484" s="3"/>
       <c r="AA484" s="1"/>
     </row>
-    <row r="485" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:27" ht="15.75" customHeight="1">
       <c r="A485" s="1" t="s">
         <v>1306</v>
       </c>
@@ -25494,7 +25496,7 @@
       <c r="U485" s="3"/>
       <c r="AA485" s="1"/>
     </row>
-    <row r="486" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:27" ht="15.75" customHeight="1">
       <c r="A486" s="1" t="s">
         <v>1307</v>
       </c>
@@ -25520,7 +25522,7 @@
       <c r="U486" s="3"/>
       <c r="AA486" s="1"/>
     </row>
-    <row r="487" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:27" ht="15.75" customHeight="1">
       <c r="A487" s="1" t="s">
         <v>1308</v>
       </c>
@@ -25546,7 +25548,7 @@
       <c r="U487" s="3"/>
       <c r="AA487" s="1"/>
     </row>
-    <row r="488" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:27" ht="15.75" customHeight="1">
       <c r="G488" s="2"/>
       <c r="K488" s="3"/>
       <c r="L488" s="3"/>
@@ -25561,7 +25563,7 @@
       <c r="U488" s="3"/>
       <c r="AA488" s="1"/>
     </row>
-    <row r="489" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:27" ht="15.75" customHeight="1">
       <c r="G489" s="2"/>
       <c r="K489" s="3"/>
       <c r="L489" s="3"/>
@@ -25576,7 +25578,7 @@
       <c r="U489" s="3"/>
       <c r="AA489" s="1"/>
     </row>
-    <row r="490" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:27" ht="15.75" customHeight="1">
       <c r="G490" s="2"/>
       <c r="K490" s="3"/>
       <c r="L490" s="3"/>
@@ -25591,7 +25593,7 @@
       <c r="U490" s="3"/>
       <c r="AA490" s="1"/>
     </row>
-    <row r="491" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:27" ht="15.75" customHeight="1">
       <c r="G491" s="2"/>
       <c r="K491" s="3"/>
       <c r="L491" s="3"/>
@@ -25606,7 +25608,7 @@
       <c r="U491" s="3"/>
       <c r="AA491" s="1"/>
     </row>
-    <row r="492" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:27" ht="15.75" customHeight="1">
       <c r="G492" s="2"/>
       <c r="K492" s="3"/>
       <c r="L492" s="3"/>
@@ -25621,7 +25623,7 @@
       <c r="U492" s="3"/>
       <c r="AA492" s="1"/>
     </row>
-    <row r="493" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:27" ht="15.75" customHeight="1">
       <c r="G493" s="2"/>
       <c r="K493" s="3"/>
       <c r="L493" s="3"/>
@@ -25636,7 +25638,7 @@
       <c r="U493" s="3"/>
       <c r="AA493" s="1"/>
     </row>
-    <row r="494" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:27" ht="15.75" customHeight="1">
       <c r="G494" s="2"/>
       <c r="K494" s="3"/>
       <c r="L494" s="3"/>
@@ -25651,7 +25653,7 @@
       <c r="U494" s="3"/>
       <c r="AA494" s="1"/>
     </row>
-    <row r="495" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:27" ht="15.75" customHeight="1">
       <c r="G495" s="2"/>
       <c r="K495" s="3"/>
       <c r="L495" s="3"/>
@@ -25666,7 +25668,7 @@
       <c r="U495" s="3"/>
       <c r="AA495" s="1"/>
     </row>
-    <row r="496" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:27" ht="15.75" customHeight="1">
       <c r="G496" s="2"/>
       <c r="K496" s="3"/>
       <c r="L496" s="3"/>
@@ -25681,7 +25683,7 @@
       <c r="U496" s="3"/>
       <c r="AA496" s="1"/>
     </row>
-    <row r="497" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="7:27" ht="15.75" customHeight="1">
       <c r="G497" s="2"/>
       <c r="K497" s="3"/>
       <c r="L497" s="3"/>
@@ -25696,7 +25698,7 @@
       <c r="U497" s="3"/>
       <c r="AA497" s="1"/>
     </row>
-    <row r="498" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="7:27" ht="15.75" customHeight="1">
       <c r="G498" s="2"/>
       <c r="K498" s="3"/>
       <c r="L498" s="3"/>
@@ -25711,7 +25713,7 @@
       <c r="U498" s="3"/>
       <c r="AA498" s="1"/>
     </row>
-    <row r="499" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="7:27" ht="15.75" customHeight="1">
       <c r="G499" s="2"/>
       <c r="K499" s="3"/>
       <c r="L499" s="3"/>
@@ -25726,7 +25728,7 @@
       <c r="U499" s="3"/>
       <c r="AA499" s="1"/>
     </row>
-    <row r="500" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="7:27" ht="15.75" customHeight="1">
       <c r="G500" s="2"/>
       <c r="K500" s="3"/>
       <c r="L500" s="3"/>
@@ -25741,7 +25743,7 @@
       <c r="U500" s="3"/>
       <c r="AA500" s="1"/>
     </row>
-    <row r="501" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="7:27" ht="15.75" customHeight="1">
       <c r="G501" s="2"/>
       <c r="K501" s="3"/>
       <c r="L501" s="3"/>
@@ -25756,7 +25758,7 @@
       <c r="U501" s="3"/>
       <c r="AA501" s="1"/>
     </row>
-    <row r="502" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="7:27" ht="15.75" customHeight="1">
       <c r="G502" s="2"/>
       <c r="K502" s="3"/>
       <c r="L502" s="3"/>
@@ -25771,7 +25773,7 @@
       <c r="U502" s="3"/>
       <c r="AA502" s="1"/>
     </row>
-    <row r="503" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="7:27" ht="15.75" customHeight="1">
       <c r="G503" s="2"/>
       <c r="K503" s="3"/>
       <c r="L503" s="3"/>
@@ -25786,7 +25788,7 @@
       <c r="U503" s="3"/>
       <c r="AA503" s="1"/>
     </row>
-    <row r="504" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="7:27" ht="15.75" customHeight="1">
       <c r="G504" s="2"/>
       <c r="K504" s="3"/>
       <c r="L504" s="3"/>
@@ -25801,7 +25803,7 @@
       <c r="U504" s="3"/>
       <c r="AA504" s="1"/>
     </row>
-    <row r="505" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="7:27" ht="15.75" customHeight="1">
       <c r="G505" s="2"/>
       <c r="K505" s="3"/>
       <c r="L505" s="3"/>
@@ -25816,7 +25818,7 @@
       <c r="U505" s="3"/>
       <c r="AA505" s="1"/>
     </row>
-    <row r="506" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="7:27" ht="15.75" customHeight="1">
       <c r="G506" s="2"/>
       <c r="K506" s="3"/>
       <c r="L506" s="3"/>
@@ -25831,7 +25833,7 @@
       <c r="U506" s="3"/>
       <c r="AA506" s="1"/>
     </row>
-    <row r="507" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="7:27" ht="15.75" customHeight="1">
       <c r="G507" s="2"/>
       <c r="K507" s="3"/>
       <c r="L507" s="3"/>
@@ -25846,7 +25848,7 @@
       <c r="U507" s="3"/>
       <c r="AA507" s="1"/>
     </row>
-    <row r="508" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="7:27" ht="15.75" customHeight="1">
       <c r="G508" s="2"/>
       <c r="K508" s="3"/>
       <c r="L508" s="3"/>
@@ -25861,7 +25863,7 @@
       <c r="U508" s="3"/>
       <c r="AA508" s="1"/>
     </row>
-    <row r="509" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="7:27" ht="15.75" customHeight="1">
       <c r="G509" s="2"/>
       <c r="K509" s="3"/>
       <c r="L509" s="3"/>
@@ -25876,7 +25878,7 @@
       <c r="U509" s="3"/>
       <c r="AA509" s="1"/>
     </row>
-    <row r="510" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="7:27" ht="15.75" customHeight="1">
       <c r="G510" s="2"/>
       <c r="K510" s="3"/>
       <c r="L510" s="3"/>
@@ -25891,7 +25893,7 @@
       <c r="U510" s="3"/>
       <c r="AA510" s="1"/>
     </row>
-    <row r="511" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="7:27" ht="15.75" customHeight="1">
       <c r="G511" s="2"/>
       <c r="K511" s="3"/>
       <c r="L511" s="3"/>
@@ -25906,7 +25908,7 @@
       <c r="U511" s="3"/>
       <c r="AA511" s="1"/>
     </row>
-    <row r="512" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="7:27" ht="15.75" customHeight="1">
       <c r="G512" s="2"/>
       <c r="K512" s="3"/>
       <c r="L512" s="3"/>
@@ -25921,7 +25923,7 @@
       <c r="U512" s="3"/>
       <c r="AA512" s="1"/>
     </row>
-    <row r="513" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="7:27" ht="15.75" customHeight="1">
       <c r="G513" s="2"/>
       <c r="K513" s="3"/>
       <c r="L513" s="3"/>
@@ -25936,7 +25938,7 @@
       <c r="U513" s="3"/>
       <c r="AA513" s="1"/>
     </row>
-    <row r="514" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="7:27" ht="15.75" customHeight="1">
       <c r="G514" s="2"/>
       <c r="K514" s="3"/>
       <c r="L514" s="3"/>
@@ -25951,7 +25953,7 @@
       <c r="U514" s="3"/>
       <c r="AA514" s="1"/>
     </row>
-    <row r="515" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="7:27" ht="15.75" customHeight="1">
       <c r="G515" s="2"/>
       <c r="K515" s="3"/>
       <c r="L515" s="3"/>
@@ -25966,7 +25968,7 @@
       <c r="U515" s="3"/>
       <c r="AA515" s="1"/>
     </row>
-    <row r="516" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="7:27" ht="15.75" customHeight="1">
       <c r="G516" s="2"/>
       <c r="K516" s="3"/>
       <c r="L516" s="3"/>
@@ -25981,7 +25983,7 @@
       <c r="U516" s="3"/>
       <c r="AA516" s="1"/>
     </row>
-    <row r="517" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="7:27" ht="15.75" customHeight="1">
       <c r="G517" s="2"/>
       <c r="K517" s="3"/>
       <c r="L517" s="3"/>
@@ -25996,7 +25998,7 @@
       <c r="U517" s="3"/>
       <c r="AA517" s="1"/>
     </row>
-    <row r="518" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="7:27" ht="15.75" customHeight="1">
       <c r="G518" s="2"/>
       <c r="K518" s="3"/>
       <c r="L518" s="3"/>
@@ -26011,7 +26013,7 @@
       <c r="U518" s="3"/>
       <c r="AA518" s="1"/>
     </row>
-    <row r="519" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="7:27" ht="15.75" customHeight="1">
       <c r="G519" s="2"/>
       <c r="K519" s="3"/>
       <c r="L519" s="3"/>
@@ -26026,7 +26028,7 @@
       <c r="U519" s="3"/>
       <c r="AA519" s="1"/>
     </row>
-    <row r="520" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="7:27" ht="15.75" customHeight="1">
       <c r="G520" s="2"/>
       <c r="K520" s="3"/>
       <c r="L520" s="3"/>
@@ -26041,7 +26043,7 @@
       <c r="U520" s="3"/>
       <c r="AA520" s="1"/>
     </row>
-    <row r="521" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="7:27" ht="15.75" customHeight="1">
       <c r="G521" s="2"/>
       <c r="K521" s="3"/>
       <c r="L521" s="3"/>
@@ -26056,7 +26058,7 @@
       <c r="U521" s="3"/>
       <c r="AA521" s="1"/>
     </row>
-    <row r="522" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="7:27" ht="15.75" customHeight="1">
       <c r="G522" s="2"/>
       <c r="K522" s="3"/>
       <c r="L522" s="3"/>
@@ -26071,7 +26073,7 @@
       <c r="U522" s="3"/>
       <c r="AA522" s="1"/>
     </row>
-    <row r="523" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="7:27" ht="15.75" customHeight="1">
       <c r="G523" s="2"/>
       <c r="K523" s="3"/>
       <c r="L523" s="3"/>
@@ -26086,7 +26088,7 @@
       <c r="U523" s="3"/>
       <c r="AA523" s="1"/>
     </row>
-    <row r="524" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="7:27" ht="15.75" customHeight="1">
       <c r="G524" s="2"/>
       <c r="K524" s="3"/>
       <c r="L524" s="3"/>
@@ -26101,7 +26103,7 @@
       <c r="U524" s="3"/>
       <c r="AA524" s="1"/>
     </row>
-    <row r="525" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="7:27" ht="15.75" customHeight="1">
       <c r="G525" s="2"/>
       <c r="K525" s="3"/>
       <c r="L525" s="3"/>
@@ -26116,7 +26118,7 @@
       <c r="U525" s="3"/>
       <c r="AA525" s="1"/>
     </row>
-    <row r="526" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="7:27" ht="15.75" customHeight="1">
       <c r="G526" s="2"/>
       <c r="K526" s="3"/>
       <c r="L526" s="3"/>
@@ -26131,7 +26133,7 @@
       <c r="U526" s="3"/>
       <c r="AA526" s="1"/>
     </row>
-    <row r="527" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="7:27" ht="15.75" customHeight="1">
       <c r="G527" s="2"/>
       <c r="K527" s="3"/>
       <c r="L527" s="3"/>
@@ -26146,7 +26148,7 @@
       <c r="U527" s="3"/>
       <c r="AA527" s="1"/>
     </row>
-    <row r="528" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="7:27" ht="15.75" customHeight="1">
       <c r="G528" s="2"/>
       <c r="K528" s="3"/>
       <c r="L528" s="3"/>
@@ -26161,7 +26163,7 @@
       <c r="U528" s="3"/>
       <c r="AA528" s="1"/>
     </row>
-    <row r="529" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="7:27" ht="15.75" customHeight="1">
       <c r="G529" s="2"/>
       <c r="K529" s="3"/>
       <c r="L529" s="3"/>
@@ -26176,7 +26178,7 @@
       <c r="U529" s="3"/>
       <c r="AA529" s="1"/>
     </row>
-    <row r="530" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="7:27" ht="15.75" customHeight="1">
       <c r="G530" s="2"/>
       <c r="K530" s="3"/>
       <c r="L530" s="3"/>
@@ -26191,7 +26193,7 @@
       <c r="U530" s="3"/>
       <c r="AA530" s="1"/>
     </row>
-    <row r="531" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="7:27" ht="15.75" customHeight="1">
       <c r="G531" s="2"/>
       <c r="K531" s="3"/>
       <c r="L531" s="3"/>
@@ -26206,7 +26208,7 @@
       <c r="U531" s="3"/>
       <c r="AA531" s="1"/>
     </row>
-    <row r="532" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="7:27" ht="15.75" customHeight="1">
       <c r="G532" s="2"/>
       <c r="K532" s="3"/>
       <c r="L532" s="3"/>
@@ -26221,7 +26223,7 @@
       <c r="U532" s="3"/>
       <c r="AA532" s="1"/>
     </row>
-    <row r="533" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="7:27" ht="15.75" customHeight="1">
       <c r="G533" s="2"/>
       <c r="K533" s="3"/>
       <c r="L533" s="3"/>
@@ -26236,7 +26238,7 @@
       <c r="U533" s="3"/>
       <c r="AA533" s="1"/>
     </row>
-    <row r="534" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="7:27" ht="15.75" customHeight="1">
       <c r="G534" s="2"/>
       <c r="K534" s="3"/>
       <c r="L534" s="3"/>
@@ -26251,7 +26253,7 @@
       <c r="U534" s="3"/>
       <c r="AA534" s="1"/>
     </row>
-    <row r="535" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="7:27" ht="15.75" customHeight="1">
       <c r="G535" s="2"/>
       <c r="K535" s="3"/>
       <c r="L535" s="3"/>
@@ -26266,7 +26268,7 @@
       <c r="U535" s="3"/>
       <c r="AA535" s="1"/>
     </row>
-    <row r="536" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="7:27" ht="15.75" customHeight="1">
       <c r="G536" s="2"/>
       <c r="K536" s="3"/>
       <c r="L536" s="3"/>
@@ -26281,7 +26283,7 @@
       <c r="U536" s="3"/>
       <c r="AA536" s="1"/>
     </row>
-    <row r="537" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="7:27" ht="15.75" customHeight="1">
       <c r="G537" s="2"/>
       <c r="K537" s="3"/>
       <c r="L537" s="3"/>
@@ -26296,7 +26298,7 @@
       <c r="U537" s="3"/>
       <c r="AA537" s="1"/>
     </row>
-    <row r="538" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="7:27" ht="15.75" customHeight="1">
       <c r="G538" s="2"/>
       <c r="K538" s="3"/>
       <c r="L538" s="3"/>
@@ -26311,7 +26313,7 @@
       <c r="U538" s="3"/>
       <c r="AA538" s="1"/>
     </row>
-    <row r="539" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="7:27" ht="15.75" customHeight="1">
       <c r="G539" s="2"/>
       <c r="K539" s="3"/>
       <c r="L539" s="3"/>
@@ -26326,7 +26328,7 @@
       <c r="U539" s="3"/>
       <c r="AA539" s="1"/>
     </row>
-    <row r="540" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="7:27" ht="15.75" customHeight="1">
       <c r="G540" s="2"/>
       <c r="K540" s="3"/>
       <c r="L540" s="3"/>
@@ -26341,7 +26343,7 @@
       <c r="U540" s="3"/>
       <c r="AA540" s="1"/>
     </row>
-    <row r="541" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="7:27" ht="15.75" customHeight="1">
       <c r="G541" s="2"/>
       <c r="K541" s="3"/>
       <c r="L541" s="3"/>
@@ -26356,7 +26358,7 @@
       <c r="U541" s="3"/>
       <c r="AA541" s="1"/>
     </row>
-    <row r="542" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="7:27" ht="15.75" customHeight="1">
       <c r="G542" s="2"/>
       <c r="K542" s="3"/>
       <c r="L542" s="3"/>
@@ -26371,7 +26373,7 @@
       <c r="U542" s="3"/>
       <c r="AA542" s="1"/>
     </row>
-    <row r="543" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="7:27" ht="15.75" customHeight="1">
       <c r="G543" s="2"/>
       <c r="K543" s="3"/>
       <c r="L543" s="3"/>
@@ -26386,7 +26388,7 @@
       <c r="U543" s="3"/>
       <c r="AA543" s="1"/>
     </row>
-    <row r="544" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="7:27" ht="15.75" customHeight="1">
       <c r="G544" s="2"/>
       <c r="K544" s="3"/>
       <c r="L544" s="3"/>
@@ -26401,7 +26403,7 @@
       <c r="U544" s="3"/>
       <c r="AA544" s="1"/>
     </row>
-    <row r="545" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="7:27" ht="15.75" customHeight="1">
       <c r="G545" s="2"/>
       <c r="K545" s="3"/>
       <c r="L545" s="3"/>
@@ -26416,7 +26418,7 @@
       <c r="U545" s="3"/>
       <c r="AA545" s="1"/>
     </row>
-    <row r="546" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="7:27" ht="15.75" customHeight="1">
       <c r="G546" s="2"/>
       <c r="K546" s="3"/>
       <c r="L546" s="3"/>
@@ -26431,7 +26433,7 @@
       <c r="U546" s="3"/>
       <c r="AA546" s="1"/>
     </row>
-    <row r="547" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="7:27" ht="15.75" customHeight="1">
       <c r="G547" s="2"/>
       <c r="K547" s="3"/>
       <c r="L547" s="3"/>
@@ -26446,7 +26448,7 @@
       <c r="U547" s="3"/>
       <c r="AA547" s="1"/>
     </row>
-    <row r="548" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="7:27" ht="15.75" customHeight="1">
       <c r="G548" s="2"/>
       <c r="K548" s="3"/>
       <c r="L548" s="3"/>
@@ -26461,7 +26463,7 @@
       <c r="U548" s="3"/>
       <c r="AA548" s="1"/>
     </row>
-    <row r="549" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="7:27" ht="15.75" customHeight="1">
       <c r="G549" s="2"/>
       <c r="K549" s="3"/>
       <c r="L549" s="3"/>
@@ -26476,7 +26478,7 @@
       <c r="U549" s="3"/>
       <c r="AA549" s="1"/>
     </row>
-    <row r="550" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="7:27" ht="15.75" customHeight="1">
       <c r="G550" s="2"/>
       <c r="K550" s="3"/>
       <c r="L550" s="3"/>
@@ -26491,7 +26493,7 @@
       <c r="U550" s="3"/>
       <c r="AA550" s="1"/>
     </row>
-    <row r="551" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="7:27" ht="15.75" customHeight="1">
       <c r="G551" s="2"/>
       <c r="K551" s="3"/>
       <c r="L551" s="3"/>
@@ -26506,7 +26508,7 @@
       <c r="U551" s="3"/>
       <c r="AA551" s="1"/>
     </row>
-    <row r="552" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="7:27" ht="15.75" customHeight="1">
       <c r="G552" s="2"/>
       <c r="K552" s="3"/>
       <c r="L552" s="3"/>
@@ -26521,7 +26523,7 @@
       <c r="U552" s="3"/>
       <c r="AA552" s="1"/>
     </row>
-    <row r="553" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="7:27" ht="15.75" customHeight="1">
       <c r="G553" s="2"/>
       <c r="K553" s="3"/>
       <c r="L553" s="3"/>
@@ -26536,7 +26538,7 @@
       <c r="U553" s="3"/>
       <c r="AA553" s="1"/>
     </row>
-    <row r="554" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="7:27" ht="15.75" customHeight="1">
       <c r="G554" s="2"/>
       <c r="K554" s="3"/>
       <c r="L554" s="3"/>
@@ -26551,7 +26553,7 @@
       <c r="U554" s="3"/>
       <c r="AA554" s="1"/>
     </row>
-    <row r="555" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="7:27" ht="15.75" customHeight="1">
       <c r="G555" s="2"/>
       <c r="K555" s="3"/>
       <c r="L555" s="3"/>
@@ -26566,7 +26568,7 @@
       <c r="U555" s="3"/>
       <c r="AA555" s="1"/>
     </row>
-    <row r="556" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="7:27" ht="15.75" customHeight="1">
       <c r="G556" s="2"/>
       <c r="K556" s="3"/>
       <c r="L556" s="3"/>
@@ -26581,7 +26583,7 @@
       <c r="U556" s="3"/>
       <c r="AA556" s="1"/>
     </row>
-    <row r="557" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="7:27" ht="15.75" customHeight="1">
       <c r="G557" s="2"/>
       <c r="K557" s="3"/>
       <c r="L557" s="3"/>
@@ -26596,7 +26598,7 @@
       <c r="U557" s="3"/>
       <c r="AA557" s="1"/>
     </row>
-    <row r="558" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="7:27" ht="15.75" customHeight="1">
       <c r="G558" s="2"/>
       <c r="K558" s="3"/>
       <c r="L558" s="3"/>
@@ -26611,7 +26613,7 @@
       <c r="U558" s="3"/>
       <c r="AA558" s="1"/>
     </row>
-    <row r="559" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="7:27" ht="15.75" customHeight="1">
       <c r="G559" s="2"/>
       <c r="K559" s="3"/>
       <c r="L559" s="3"/>
@@ -26626,7 +26628,7 @@
       <c r="U559" s="3"/>
       <c r="AA559" s="1"/>
     </row>
-    <row r="560" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="7:27" ht="15.75" customHeight="1">
       <c r="G560" s="2"/>
       <c r="K560" s="3"/>
       <c r="L560" s="3"/>
@@ -26641,7 +26643,7 @@
       <c r="U560" s="3"/>
       <c r="AA560" s="1"/>
     </row>
-    <row r="561" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="7:27" ht="15.75" customHeight="1">
       <c r="G561" s="2"/>
       <c r="K561" s="3"/>
       <c r="L561" s="3"/>
@@ -26656,7 +26658,7 @@
       <c r="U561" s="3"/>
       <c r="AA561" s="1"/>
     </row>
-    <row r="562" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="7:27" ht="15.75" customHeight="1">
       <c r="G562" s="2"/>
       <c r="K562" s="3"/>
       <c r="L562" s="3"/>
@@ -26671,7 +26673,7 @@
       <c r="U562" s="3"/>
       <c r="AA562" s="1"/>
     </row>
-    <row r="563" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="7:27" ht="15.75" customHeight="1">
       <c r="G563" s="2"/>
       <c r="K563" s="3"/>
       <c r="L563" s="3"/>
@@ -26686,7 +26688,7 @@
       <c r="U563" s="3"/>
       <c r="AA563" s="1"/>
     </row>
-    <row r="564" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="7:27" ht="15.75" customHeight="1">
       <c r="G564" s="2"/>
       <c r="K564" s="3"/>
       <c r="L564" s="3"/>
@@ -26701,7 +26703,7 @@
       <c r="U564" s="3"/>
       <c r="AA564" s="1"/>
     </row>
-    <row r="565" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="7:27" ht="15.75" customHeight="1">
       <c r="G565" s="2"/>
       <c r="K565" s="3"/>
       <c r="L565" s="3"/>
@@ -26716,7 +26718,7 @@
       <c r="U565" s="3"/>
       <c r="AA565" s="1"/>
     </row>
-    <row r="566" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="7:27" ht="15.75" customHeight="1">
       <c r="G566" s="2"/>
       <c r="K566" s="3"/>
       <c r="L566" s="3"/>
@@ -26731,7 +26733,7 @@
       <c r="U566" s="3"/>
       <c r="AA566" s="1"/>
     </row>
-    <row r="567" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="7:27" ht="15.75" customHeight="1">
       <c r="G567" s="2"/>
       <c r="K567" s="3"/>
       <c r="L567" s="3"/>
@@ -26746,7 +26748,7 @@
       <c r="U567" s="3"/>
       <c r="AA567" s="1"/>
     </row>
-    <row r="568" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="7:27" ht="15.75" customHeight="1">
       <c r="G568" s="2"/>
       <c r="K568" s="3"/>
       <c r="L568" s="3"/>
@@ -26761,7 +26763,7 @@
       <c r="U568" s="3"/>
       <c r="AA568" s="1"/>
     </row>
-    <row r="569" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="7:27" ht="15.75" customHeight="1">
       <c r="G569" s="2"/>
       <c r="K569" s="3"/>
       <c r="L569" s="3"/>
@@ -26776,7 +26778,7 @@
       <c r="U569" s="3"/>
       <c r="AA569" s="1"/>
     </row>
-    <row r="570" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="7:27" ht="15.75" customHeight="1">
       <c r="G570" s="2"/>
       <c r="K570" s="3"/>
       <c r="L570" s="3"/>
@@ -26791,7 +26793,7 @@
       <c r="U570" s="3"/>
       <c r="AA570" s="1"/>
     </row>
-    <row r="571" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="7:27" ht="15.75" customHeight="1">
       <c r="G571" s="2"/>
       <c r="K571" s="3"/>
       <c r="L571" s="3"/>
@@ -26806,7 +26808,7 @@
       <c r="U571" s="3"/>
       <c r="AA571" s="1"/>
     </row>
-    <row r="572" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="7:27" ht="15.75" customHeight="1">
       <c r="G572" s="2"/>
       <c r="K572" s="3"/>
       <c r="L572" s="3"/>
@@ -26821,7 +26823,7 @@
       <c r="U572" s="3"/>
       <c r="AA572" s="1"/>
     </row>
-    <row r="573" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="7:27" ht="15.75" customHeight="1">
       <c r="G573" s="2"/>
       <c r="K573" s="3"/>
       <c r="L573" s="3"/>
@@ -26836,7 +26838,7 @@
       <c r="U573" s="3"/>
       <c r="AA573" s="1"/>
     </row>
-    <row r="574" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="7:27" ht="15.75" customHeight="1">
       <c r="G574" s="2"/>
       <c r="K574" s="3"/>
       <c r="L574" s="3"/>
@@ -26851,7 +26853,7 @@
       <c r="U574" s="3"/>
       <c r="AA574" s="1"/>
     </row>
-    <row r="575" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="7:27" ht="15.75" customHeight="1">
       <c r="G575" s="2"/>
       <c r="K575" s="3"/>
       <c r="L575" s="3"/>
@@ -26866,7 +26868,7 @@
       <c r="U575" s="3"/>
       <c r="AA575" s="1"/>
     </row>
-    <row r="576" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="7:27" ht="15.75" customHeight="1">
       <c r="G576" s="2"/>
       <c r="K576" s="3"/>
       <c r="L576" s="3"/>
@@ -26881,7 +26883,7 @@
       <c r="U576" s="3"/>
       <c r="AA576" s="1"/>
     </row>
-    <row r="577" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="7:27" ht="15.75" customHeight="1">
       <c r="G577" s="2"/>
       <c r="K577" s="3"/>
       <c r="L577" s="3"/>
@@ -26896,7 +26898,7 @@
       <c r="U577" s="3"/>
       <c r="AA577" s="1"/>
     </row>
-    <row r="578" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="7:27" ht="15.75" customHeight="1">
       <c r="G578" s="2"/>
       <c r="K578" s="3"/>
       <c r="L578" s="3"/>
@@ -26911,7 +26913,7 @@
       <c r="U578" s="3"/>
       <c r="AA578" s="1"/>
     </row>
-    <row r="579" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="7:27" ht="15.75" customHeight="1">
       <c r="G579" s="2"/>
       <c r="K579" s="3"/>
       <c r="L579" s="3"/>
@@ -26926,7 +26928,7 @@
       <c r="U579" s="3"/>
       <c r="AA579" s="1"/>
     </row>
-    <row r="580" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="7:27" ht="15.75" customHeight="1">
       <c r="G580" s="2"/>
       <c r="K580" s="3"/>
       <c r="L580" s="3"/>
@@ -26941,7 +26943,7 @@
       <c r="U580" s="3"/>
       <c r="AA580" s="1"/>
     </row>
-    <row r="581" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="7:27" ht="15.75" customHeight="1">
       <c r="G581" s="2"/>
       <c r="K581" s="3"/>
       <c r="L581" s="3"/>
@@ -26956,7 +26958,7 @@
       <c r="U581" s="3"/>
       <c r="AA581" s="1"/>
     </row>
-    <row r="582" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="7:27" ht="15.75" customHeight="1">
       <c r="G582" s="2"/>
       <c r="K582" s="3"/>
       <c r="L582" s="3"/>
@@ -26971,7 +26973,7 @@
       <c r="U582" s="3"/>
       <c r="AA582" s="1"/>
     </row>
-    <row r="583" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="7:27" ht="15.75" customHeight="1">
       <c r="G583" s="2"/>
       <c r="K583" s="3"/>
       <c r="L583" s="3"/>
@@ -26986,7 +26988,7 @@
       <c r="U583" s="3"/>
       <c r="AA583" s="1"/>
     </row>
-    <row r="584" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="7:27" ht="15.75" customHeight="1">
       <c r="G584" s="2"/>
       <c r="K584" s="3"/>
       <c r="L584" s="3"/>
@@ -27001,7 +27003,7 @@
       <c r="U584" s="3"/>
       <c r="AA584" s="1"/>
     </row>
-    <row r="585" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="7:27" ht="15.75" customHeight="1">
       <c r="G585" s="2"/>
       <c r="K585" s="3"/>
       <c r="L585" s="3"/>
@@ -27016,7 +27018,7 @@
       <c r="U585" s="3"/>
       <c r="AA585" s="1"/>
     </row>
-    <row r="586" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="7:27" ht="15.75" customHeight="1">
       <c r="G586" s="2"/>
       <c r="K586" s="3"/>
       <c r="L586" s="3"/>
@@ -27031,7 +27033,7 @@
       <c r="U586" s="3"/>
       <c r="AA586" s="1"/>
     </row>
-    <row r="587" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="7:27" ht="15.75" customHeight="1">
       <c r="G587" s="2"/>
       <c r="K587" s="3"/>
       <c r="L587" s="3"/>
@@ -27046,7 +27048,7 @@
       <c r="U587" s="3"/>
       <c r="AA587" s="1"/>
     </row>
-    <row r="588" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="7:27" ht="15.75" customHeight="1">
       <c r="G588" s="2"/>
       <c r="K588" s="3"/>
       <c r="L588" s="3"/>
@@ -27061,7 +27063,7 @@
       <c r="U588" s="3"/>
       <c r="AA588" s="1"/>
     </row>
-    <row r="589" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="7:27" ht="15.75" customHeight="1">
       <c r="G589" s="2"/>
       <c r="K589" s="3"/>
       <c r="L589" s="3"/>
@@ -27076,7 +27078,7 @@
       <c r="U589" s="3"/>
       <c r="AA589" s="1"/>
     </row>
-    <row r="590" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="7:27" ht="15.75" customHeight="1">
       <c r="G590" s="2"/>
       <c r="K590" s="3"/>
       <c r="L590" s="3"/>
@@ -27091,7 +27093,7 @@
       <c r="U590" s="3"/>
       <c r="AA590" s="1"/>
     </row>
-    <row r="591" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="7:27" ht="15.75" customHeight="1">
       <c r="G591" s="2"/>
       <c r="K591" s="3"/>
       <c r="L591" s="3"/>
@@ -27106,7 +27108,7 @@
       <c r="U591" s="3"/>
       <c r="AA591" s="1"/>
     </row>
-    <row r="592" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="7:27" ht="15.75" customHeight="1">
       <c r="G592" s="2"/>
       <c r="K592" s="3"/>
       <c r="L592" s="3"/>
@@ -27121,7 +27123,7 @@
       <c r="U592" s="3"/>
       <c r="AA592" s="1"/>
     </row>
-    <row r="593" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="7:27" ht="15.75" customHeight="1">
       <c r="G593" s="2"/>
       <c r="K593" s="3"/>
       <c r="L593" s="3"/>
@@ -27136,7 +27138,7 @@
       <c r="U593" s="3"/>
       <c r="AA593" s="1"/>
     </row>
-    <row r="594" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="7:27" ht="15.75" customHeight="1">
       <c r="G594" s="2"/>
       <c r="K594" s="3"/>
       <c r="L594" s="3"/>
@@ -27151,7 +27153,7 @@
       <c r="U594" s="3"/>
       <c r="AA594" s="1"/>
     </row>
-    <row r="595" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="7:27" ht="15.75" customHeight="1">
       <c r="G595" s="2"/>
       <c r="K595" s="3"/>
       <c r="L595" s="3"/>
@@ -27166,7 +27168,7 @@
       <c r="U595" s="3"/>
       <c r="AA595" s="1"/>
     </row>
-    <row r="596" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="7:27" ht="15.75" customHeight="1">
       <c r="G596" s="2"/>
       <c r="K596" s="3"/>
       <c r="L596" s="3"/>
@@ -27181,7 +27183,7 @@
       <c r="U596" s="3"/>
       <c r="AA596" s="1"/>
     </row>
-    <row r="597" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="7:27" ht="15.75" customHeight="1">
       <c r="G597" s="2"/>
       <c r="K597" s="3"/>
       <c r="L597" s="3"/>
@@ -27196,7 +27198,7 @@
       <c r="U597" s="3"/>
       <c r="AA597" s="1"/>
     </row>
-    <row r="598" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="7:27" ht="15.75" customHeight="1">
       <c r="G598" s="2"/>
       <c r="K598" s="3"/>
       <c r="L598" s="3"/>
@@ -27211,7 +27213,7 @@
       <c r="U598" s="3"/>
       <c r="AA598" s="1"/>
     </row>
-    <row r="599" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="7:27" ht="15.75" customHeight="1">
       <c r="G599" s="2"/>
       <c r="K599" s="3"/>
       <c r="L599" s="3"/>
@@ -27226,7 +27228,7 @@
       <c r="U599" s="3"/>
       <c r="AA599" s="1"/>
     </row>
-    <row r="600" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="7:27" ht="15.75" customHeight="1">
       <c r="G600" s="2"/>
       <c r="K600" s="3"/>
       <c r="L600" s="3"/>
@@ -27241,7 +27243,7 @@
       <c r="U600" s="3"/>
       <c r="AA600" s="1"/>
     </row>
-    <row r="601" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="7:27" ht="15.75" customHeight="1">
       <c r="G601" s="2"/>
       <c r="K601" s="3"/>
       <c r="L601" s="3"/>
@@ -27256,7 +27258,7 @@
       <c r="U601" s="3"/>
       <c r="AA601" s="1"/>
     </row>
-    <row r="602" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="7:27" ht="15.75" customHeight="1">
       <c r="G602" s="2"/>
       <c r="K602" s="3"/>
       <c r="L602" s="3"/>
@@ -27271,7 +27273,7 @@
       <c r="U602" s="3"/>
       <c r="AA602" s="1"/>
     </row>
-    <row r="603" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="7:27" ht="15.75" customHeight="1">
       <c r="G603" s="2"/>
       <c r="K603" s="3"/>
       <c r="L603" s="3"/>
@@ -27286,7 +27288,7 @@
       <c r="U603" s="3"/>
       <c r="AA603" s="1"/>
     </row>
-    <row r="604" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="7:27" ht="15.75" customHeight="1">
       <c r="G604" s="2"/>
       <c r="K604" s="3"/>
       <c r="L604" s="3"/>
@@ -27301,7 +27303,7 @@
       <c r="U604" s="3"/>
       <c r="AA604" s="1"/>
     </row>
-    <row r="605" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="7:27" ht="15.75" customHeight="1">
       <c r="G605" s="2"/>
       <c r="K605" s="3"/>
       <c r="L605" s="3"/>
@@ -27316,7 +27318,7 @@
       <c r="U605" s="3"/>
       <c r="AA605" s="1"/>
     </row>
-    <row r="606" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="7:27" ht="15.75" customHeight="1">
       <c r="G606" s="2"/>
       <c r="K606" s="3"/>
       <c r="L606" s="3"/>
@@ -27331,7 +27333,7 @@
       <c r="U606" s="3"/>
       <c r="AA606" s="1"/>
     </row>
-    <row r="607" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="7:27" ht="15.75" customHeight="1">
       <c r="G607" s="2"/>
       <c r="K607" s="3"/>
       <c r="L607" s="3"/>
@@ -27346,7 +27348,7 @@
       <c r="U607" s="3"/>
       <c r="AA607" s="1"/>
     </row>
-    <row r="608" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="7:27" ht="15.75" customHeight="1">
       <c r="G608" s="2"/>
       <c r="K608" s="3"/>
       <c r="L608" s="3"/>
@@ -27361,7 +27363,7 @@
       <c r="U608" s="3"/>
       <c r="AA608" s="1"/>
     </row>
-    <row r="609" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="7:27" ht="15.75" customHeight="1">
       <c r="G609" s="2"/>
       <c r="K609" s="3"/>
       <c r="L609" s="3"/>
@@ -27376,7 +27378,7 @@
       <c r="U609" s="3"/>
       <c r="AA609" s="1"/>
     </row>
-    <row r="610" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="7:27" ht="15.75" customHeight="1">
       <c r="G610" s="2"/>
       <c r="K610" s="3"/>
       <c r="L610" s="3"/>
@@ -27391,7 +27393,7 @@
       <c r="U610" s="3"/>
       <c r="AA610" s="1"/>
     </row>
-    <row r="611" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="7:27" ht="15.75" customHeight="1">
       <c r="G611" s="2"/>
       <c r="K611" s="3"/>
       <c r="L611" s="3"/>
@@ -27406,7 +27408,7 @@
       <c r="U611" s="3"/>
       <c r="AA611" s="1"/>
     </row>
-    <row r="612" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="7:27" ht="15.75" customHeight="1">
       <c r="G612" s="2"/>
       <c r="K612" s="3"/>
       <c r="L612" s="3"/>
@@ -27421,7 +27423,7 @@
       <c r="U612" s="3"/>
       <c r="AA612" s="1"/>
     </row>
-    <row r="613" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="7:27" ht="15.75" customHeight="1">
       <c r="G613" s="2"/>
       <c r="K613" s="3"/>
       <c r="L613" s="3"/>
@@ -27436,7 +27438,7 @@
       <c r="U613" s="3"/>
       <c r="AA613" s="1"/>
     </row>
-    <row r="614" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="7:27" ht="15.75" customHeight="1">
       <c r="G614" s="2"/>
       <c r="K614" s="3"/>
       <c r="L614" s="3"/>
@@ -27451,7 +27453,7 @@
       <c r="U614" s="3"/>
       <c r="AA614" s="1"/>
     </row>
-    <row r="615" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="7:27" ht="15.75" customHeight="1">
       <c r="G615" s="2"/>
       <c r="K615" s="3"/>
       <c r="L615" s="3"/>
@@ -27466,7 +27468,7 @@
       <c r="U615" s="3"/>
       <c r="AA615" s="1"/>
     </row>
-    <row r="616" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="7:27" ht="15.75" customHeight="1">
       <c r="G616" s="2"/>
       <c r="K616" s="3"/>
       <c r="L616" s="3"/>
@@ -27481,7 +27483,7 @@
       <c r="U616" s="3"/>
       <c r="AA616" s="1"/>
     </row>
-    <row r="617" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="7:27" ht="15.75" customHeight="1">
       <c r="G617" s="2"/>
       <c r="K617" s="3"/>
       <c r="L617" s="3"/>
@@ -27496,7 +27498,7 @@
       <c r="U617" s="3"/>
       <c r="AA617" s="1"/>
     </row>
-    <row r="618" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="7:27" ht="15.75" customHeight="1">
       <c r="G618" s="2"/>
       <c r="K618" s="3"/>
       <c r="L618" s="3"/>
@@ -27511,7 +27513,7 @@
       <c r="U618" s="3"/>
       <c r="AA618" s="1"/>
     </row>
-    <row r="619" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="7:27" ht="15.75" customHeight="1">
       <c r="G619" s="2"/>
       <c r="K619" s="3"/>
       <c r="L619" s="3"/>
@@ -27526,7 +27528,7 @@
       <c r="U619" s="3"/>
       <c r="AA619" s="1"/>
     </row>
-    <row r="620" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="7:27" ht="15.75" customHeight="1">
       <c r="G620" s="2"/>
       <c r="K620" s="3"/>
       <c r="L620" s="3"/>
@@ -27541,7 +27543,7 @@
       <c r="U620" s="3"/>
       <c r="AA620" s="1"/>
     </row>
-    <row r="621" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="7:27" ht="15.75" customHeight="1">
       <c r="G621" s="2"/>
       <c r="K621" s="3"/>
       <c r="L621" s="3"/>
@@ -27556,7 +27558,7 @@
       <c r="U621" s="3"/>
       <c r="AA621" s="1"/>
     </row>
-    <row r="622" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="7:27" ht="15.75" customHeight="1">
       <c r="G622" s="2"/>
       <c r="K622" s="3"/>
       <c r="L622" s="3"/>
@@ -27571,7 +27573,7 @@
       <c r="U622" s="3"/>
       <c r="AA622" s="1"/>
     </row>
-    <row r="623" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="7:27" ht="15.75" customHeight="1">
       <c r="G623" s="2"/>
       <c r="K623" s="3"/>
       <c r="L623" s="3"/>
@@ -27586,7 +27588,7 @@
       <c r="U623" s="3"/>
       <c r="AA623" s="1"/>
     </row>
-    <row r="624" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="7:27" ht="15.75" customHeight="1">
       <c r="G624" s="2"/>
       <c r="K624" s="3"/>
       <c r="L624" s="3"/>
@@ -27601,7 +27603,7 @@
       <c r="U624" s="3"/>
       <c r="AA624" s="1"/>
     </row>
-    <row r="625" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="7:27" ht="15.75" customHeight="1">
       <c r="G625" s="2"/>
       <c r="K625" s="3"/>
       <c r="L625" s="3"/>
@@ -27616,7 +27618,7 @@
       <c r="U625" s="3"/>
       <c r="AA625" s="1"/>
     </row>
-    <row r="626" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="7:27" ht="15.75" customHeight="1">
       <c r="G626" s="2"/>
       <c r="K626" s="3"/>
       <c r="L626" s="3"/>
@@ -27631,7 +27633,7 @@
       <c r="U626" s="3"/>
       <c r="AA626" s="1"/>
     </row>
-    <row r="627" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="7:27" ht="15.75" customHeight="1">
       <c r="G627" s="2"/>
       <c r="K627" s="3"/>
       <c r="L627" s="3"/>
@@ -27646,7 +27648,7 @@
       <c r="U627" s="3"/>
       <c r="AA627" s="1"/>
     </row>
-    <row r="628" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="7:27" ht="15.75" customHeight="1">
       <c r="G628" s="2"/>
       <c r="K628" s="3"/>
       <c r="L628" s="3"/>
@@ -27661,7 +27663,7 @@
       <c r="U628" s="3"/>
       <c r="AA628" s="1"/>
     </row>
-    <row r="629" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="7:27" ht="15.75" customHeight="1">
       <c r="G629" s="2"/>
       <c r="K629" s="3"/>
       <c r="L629" s="3"/>
@@ -27676,7 +27678,7 @@
       <c r="U629" s="3"/>
       <c r="AA629" s="1"/>
     </row>
-    <row r="630" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="7:27" ht="15.75" customHeight="1">
       <c r="G630" s="2"/>
       <c r="K630" s="3"/>
       <c r="L630" s="3"/>
@@ -27691,7 +27693,7 @@
       <c r="U630" s="3"/>
       <c r="AA630" s="1"/>
     </row>
-    <row r="631" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="7:27" ht="15.75" customHeight="1">
       <c r="G631" s="2"/>
       <c r="K631" s="3"/>
       <c r="L631" s="3"/>
@@ -27706,7 +27708,7 @@
       <c r="U631" s="3"/>
       <c r="AA631" s="1"/>
     </row>
-    <row r="632" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="7:27" ht="15.75" customHeight="1">
       <c r="G632" s="2"/>
       <c r="K632" s="3"/>
       <c r="L632" s="3"/>
@@ -27721,7 +27723,7 @@
       <c r="U632" s="3"/>
       <c r="AA632" s="1"/>
     </row>
-    <row r="633" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="7:27" ht="15.75" customHeight="1">
       <c r="G633" s="2"/>
       <c r="K633" s="3"/>
       <c r="L633" s="3"/>
@@ -27736,7 +27738,7 @@
       <c r="U633" s="3"/>
       <c r="AA633" s="1"/>
     </row>
-    <row r="634" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="7:27" ht="15.75" customHeight="1">
       <c r="G634" s="2"/>
       <c r="K634" s="3"/>
       <c r="L634" s="3"/>
@@ -27751,7 +27753,7 @@
       <c r="U634" s="3"/>
       <c r="AA634" s="1"/>
     </row>
-    <row r="635" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="7:27" ht="15.75" customHeight="1">
       <c r="G635" s="2"/>
       <c r="K635" s="3"/>
       <c r="L635" s="3"/>
@@ -27766,7 +27768,7 @@
       <c r="U635" s="3"/>
       <c r="AA635" s="1"/>
     </row>
-    <row r="636" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="7:27" ht="15.75" customHeight="1">
       <c r="G636" s="2"/>
       <c r="K636" s="3"/>
       <c r="L636" s="3"/>
@@ -27781,7 +27783,7 @@
       <c r="U636" s="3"/>
       <c r="AA636" s="1"/>
     </row>
-    <row r="637" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="7:27" ht="15.75" customHeight="1">
       <c r="G637" s="2"/>
       <c r="K637" s="3"/>
       <c r="L637" s="3"/>
@@ -27796,7 +27798,7 @@
       <c r="U637" s="3"/>
       <c r="AA637" s="1"/>
     </row>
-    <row r="638" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="7:27" ht="15.75" customHeight="1">
       <c r="G638" s="2"/>
       <c r="K638" s="3"/>
       <c r="L638" s="3"/>
@@ -27811,7 +27813,7 @@
       <c r="U638" s="3"/>
       <c r="AA638" s="1"/>
     </row>
-    <row r="639" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="7:27" ht="15.75" customHeight="1">
       <c r="G639" s="2"/>
       <c r="K639" s="3"/>
       <c r="L639" s="3"/>
@@ -27826,7 +27828,7 @@
       <c r="U639" s="3"/>
       <c r="AA639" s="1"/>
     </row>
-    <row r="640" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="7:27" ht="15.75" customHeight="1">
       <c r="G640" s="2"/>
       <c r="K640" s="3"/>
       <c r="L640" s="3"/>
@@ -27841,7 +27843,7 @@
       <c r="U640" s="3"/>
       <c r="AA640" s="1"/>
     </row>
-    <row r="641" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="7:27" ht="15.75" customHeight="1">
       <c r="G641" s="2"/>
       <c r="K641" s="3"/>
       <c r="L641" s="3"/>
@@ -27856,7 +27858,7 @@
       <c r="U641" s="3"/>
       <c r="AA641" s="1"/>
     </row>
-    <row r="642" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="7:27" ht="15.75" customHeight="1">
       <c r="G642" s="2"/>
       <c r="K642" s="3"/>
       <c r="L642" s="3"/>
@@ -27871,7 +27873,7 @@
       <c r="U642" s="3"/>
       <c r="AA642" s="1"/>
     </row>
-    <row r="643" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="7:27" ht="15.75" customHeight="1">
       <c r="G643" s="2"/>
       <c r="K643" s="3"/>
       <c r="L643" s="3"/>
@@ -27886,7 +27888,7 @@
       <c r="U643" s="3"/>
       <c r="AA643" s="1"/>
     </row>
-    <row r="644" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="7:27" ht="15.75" customHeight="1">
       <c r="G644" s="2"/>
       <c r="K644" s="3"/>
       <c r="L644" s="3"/>
@@ -27901,7 +27903,7 @@
       <c r="U644" s="3"/>
       <c r="AA644" s="1"/>
     </row>
-    <row r="645" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="7:27" ht="15.75" customHeight="1">
       <c r="G645" s="2"/>
       <c r="K645" s="3"/>
       <c r="L645" s="3"/>
@@ -27916,7 +27918,7 @@
       <c r="U645" s="3"/>
       <c r="AA645" s="1"/>
     </row>
-    <row r="646" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="7:27" ht="15.75" customHeight="1">
       <c r="G646" s="2"/>
       <c r="K646" s="3"/>
       <c r="L646" s="3"/>
@@ -27931,7 +27933,7 @@
       <c r="U646" s="3"/>
       <c r="AA646" s="1"/>
     </row>
-    <row r="647" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="7:27" ht="15.75" customHeight="1">
       <c r="G647" s="2"/>
       <c r="K647" s="3"/>
       <c r="L647" s="3"/>
@@ -27946,7 +27948,7 @@
       <c r="U647" s="3"/>
       <c r="AA647" s="1"/>
     </row>
-    <row r="648" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="7:27" ht="15.75" customHeight="1">
       <c r="G648" s="2"/>
       <c r="K648" s="3"/>
       <c r="L648" s="3"/>
@@ -27961,7 +27963,7 @@
       <c r="U648" s="3"/>
       <c r="AA648" s="1"/>
     </row>
-    <row r="649" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="7:27" ht="15.75" customHeight="1">
       <c r="G649" s="2"/>
       <c r="K649" s="3"/>
       <c r="L649" s="3"/>
@@ -27976,7 +27978,7 @@
       <c r="U649" s="3"/>
       <c r="AA649" s="1"/>
     </row>
-    <row r="650" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="7:27" ht="15.75" customHeight="1">
       <c r="G650" s="2"/>
       <c r="K650" s="3"/>
       <c r="L650" s="3"/>
@@ -27991,7 +27993,7 @@
       <c r="U650" s="3"/>
       <c r="AA650" s="1"/>
     </row>
-    <row r="651" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="7:27" ht="15.75" customHeight="1">
       <c r="G651" s="2"/>
       <c r="K651" s="3"/>
       <c r="L651" s="3"/>
@@ -28006,7 +28008,7 @@
       <c r="U651" s="3"/>
       <c r="AA651" s="1"/>
     </row>
-    <row r="652" spans="7:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="7:27" ht="15.75" customHeight="1">
       <c r="G652" s="2"/>
       <c r="K652" s="3"/>
       <c r="L652" s="3"/>
